--- a/MR_UKBiobank/BinaryData/Phenotyping.xlsx
+++ b/MR_UKBiobank/BinaryData/Phenotyping.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UK_Biobank_dataset\vers7\Sclerostin_vs_CVD_MR\MR_UKBiobank\BinaryData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\martaa\Documents\GitHub\MR_Sclerostin\MR_UKBiobank\BinaryData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B91B592-F3D7-4996-94FB-CB578709DAB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED9C928-F7EB-4C9A-B582-E1A0B89C501F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9698" yWindow="442" windowWidth="14400" windowHeight="8393" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2925" yWindow="3165" windowWidth="21600" windowHeight="12735" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAD" sheetId="8" r:id="rId1"/>
@@ -4223,16 +4223,15 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4253,13 +4252,37 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4271,6 +4294,24 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4280,16 +4321,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4325,8 +4369,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4343,63 +4393,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5031,21 +5031,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6B7E55-058A-4869-86D9-59F194B743A8}">
   <dimension ref="A1:AA10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.1328125" customWidth="1"/>
-    <col min="3" max="3" width="38.73046875" customWidth="1"/>
-    <col min="6" max="6" width="13.1328125" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="11" max="11" width="9.1328125" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="94" t="s">
+    <row r="1" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="105" t="s">
         <v>1109</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
       <c r="D1" s="86" t="s">
         <v>1130</v>
       </c>
@@ -5057,17 +5057,17 @@
       </c>
       <c r="I1" s="71"/>
     </row>
-    <row r="2" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="95" t="s">
+    <row r="2" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="106" t="s">
         <v>1107</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="97"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="108"/>
       <c r="F2" s="82"/>
       <c r="G2" s="82"/>
       <c r="I2" s="71"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="30" t="s">
         <v>95</v>
       </c>
@@ -5079,7 +5079,7 @@
       <c r="G3" s="72"/>
       <c r="I3" s="71"/>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>586</v>
       </c>
@@ -5087,7 +5087,7 @@
       <c r="C4" s="13" t="s">
         <v>587</v>
       </c>
-      <c r="D4" s="135">
+      <c r="D4" s="94">
         <v>35531</v>
       </c>
       <c r="E4" t="s">
@@ -5100,35 +5100,35 @@
       <c r="H4" s="83"/>
       <c r="I4" s="83"/>
     </row>
-    <row r="5" spans="1:27" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="95" t="s">
+    <row r="5" spans="1:27" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="106" t="s">
         <v>1108</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="97"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="108"/>
       <c r="G5" s="85"/>
       <c r="H5" s="78"/>
       <c r="I5" s="73"/>
-      <c r="L5" s="152" t="s">
+      <c r="L5" s="96" t="s">
         <v>1130</v>
       </c>
-      <c r="M5" s="153"/>
-      <c r="N5" s="153"/>
-      <c r="O5" s="154"/>
-      <c r="R5" s="152" t="s">
+      <c r="M5" s="97"/>
+      <c r="N5" s="97"/>
+      <c r="O5" s="98"/>
+      <c r="R5" s="96" t="s">
         <v>1144</v>
       </c>
-      <c r="S5" s="153"/>
-      <c r="T5" s="153"/>
-      <c r="U5" s="154"/>
-      <c r="X5" s="152" t="s">
+      <c r="S5" s="97"/>
+      <c r="T5" s="97"/>
+      <c r="U5" s="98"/>
+      <c r="X5" s="96" t="s">
         <v>1145</v>
       </c>
-      <c r="Y5" s="153"/>
-      <c r="Z5" s="153"/>
-      <c r="AA5" s="154"/>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="Y5" s="97"/>
+      <c r="Z5" s="97"/>
+      <c r="AA5" s="98"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>96</v>
       </c>
@@ -5141,32 +5141,32 @@
       <c r="G6" s="85"/>
       <c r="H6" s="84"/>
       <c r="I6" s="85"/>
-      <c r="L6" s="98" t="s">
+      <c r="L6" s="99" t="s">
         <v>1109</v>
       </c>
-      <c r="M6" s="99"/>
-      <c r="N6" s="102" t="s">
+      <c r="M6" s="100"/>
+      <c r="N6" s="103" t="s">
         <v>1137</v>
       </c>
-      <c r="O6" s="99"/>
-      <c r="R6" s="98" t="s">
+      <c r="O6" s="100"/>
+      <c r="R6" s="99" t="s">
         <v>1109</v>
       </c>
-      <c r="S6" s="99"/>
-      <c r="T6" s="102" t="s">
+      <c r="S6" s="100"/>
+      <c r="T6" s="103" t="s">
         <v>1153</v>
       </c>
-      <c r="U6" s="99"/>
-      <c r="X6" s="98" t="s">
+      <c r="U6" s="100"/>
+      <c r="X6" s="99" t="s">
         <v>1109</v>
       </c>
-      <c r="Y6" s="99"/>
-      <c r="Z6" s="102" t="s">
+      <c r="Y6" s="100"/>
+      <c r="Z6" s="103" t="s">
         <v>1154</v>
       </c>
-      <c r="AA6" s="99"/>
-    </row>
-    <row r="7" spans="1:27" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="AA6" s="100"/>
+    </row>
+    <row r="7" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>588</v>
       </c>
@@ -5176,7 +5176,7 @@
       <c r="C7" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="D7" s="135">
+      <c r="D7" s="94">
         <v>735</v>
       </c>
       <c r="E7" t="s">
@@ -5186,26 +5186,26 @@
         <v>1125</v>
       </c>
       <c r="G7" s="75"/>
-      <c r="L7" s="100"/>
-      <c r="M7" s="101"/>
-      <c r="N7" s="103">
+      <c r="L7" s="101"/>
+      <c r="M7" s="102"/>
+      <c r="N7" s="104">
         <v>8.0600000000000005E-2</v>
       </c>
-      <c r="O7" s="101"/>
-      <c r="R7" s="100"/>
-      <c r="S7" s="101"/>
-      <c r="T7" s="103">
+      <c r="O7" s="102"/>
+      <c r="R7" s="101"/>
+      <c r="S7" s="102"/>
+      <c r="T7" s="104">
         <v>8.0600000000000005E-2</v>
       </c>
-      <c r="U7" s="101"/>
-      <c r="X7" s="100"/>
-      <c r="Y7" s="101"/>
-      <c r="Z7" s="103">
+      <c r="U7" s="102"/>
+      <c r="X7" s="101"/>
+      <c r="Y7" s="102"/>
+      <c r="Z7" s="104">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="AA7" s="101"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AA7" s="102"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>590</v>
       </c>
@@ -5215,7 +5215,7 @@
       <c r="C8" s="9" t="s">
         <v>591</v>
       </c>
-      <c r="D8" s="135">
+      <c r="D8" s="94">
         <v>0</v>
       </c>
       <c r="E8" t="s">
@@ -5225,7 +5225,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>592</v>
       </c>
@@ -5235,7 +5235,7 @@
       <c r="C9" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="D9" s="135">
+      <c r="D9" s="94">
         <v>221</v>
       </c>
       <c r="E9" t="s">
@@ -5245,7 +5245,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>594</v>
       </c>
@@ -5255,7 +5255,7 @@
       <c r="C10" s="14" t="s">
         <v>595</v>
       </c>
-      <c r="D10" s="135">
+      <c r="D10" s="94">
         <v>3</v>
       </c>
       <c r="E10" t="s">
@@ -5267,6 +5267,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="L6:M7"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="L5:O5"/>
     <mergeCell ref="R5:U5"/>
     <mergeCell ref="R6:S7"/>
     <mergeCell ref="T6:U6"/>
@@ -5275,13 +5282,6 @@
     <mergeCell ref="X6:Y7"/>
     <mergeCell ref="Z6:AA6"/>
     <mergeCell ref="Z7:AA7"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="L6:M7"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="L5:O5"/>
   </mergeCells>
   <conditionalFormatting sqref="E2:E10">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
@@ -5307,17 +5307,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D562CD95-4F52-4DBA-B00F-BE395EA14FCC}">
   <dimension ref="A1:AD282"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="61" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:30" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="122" t="s">
         <v>1110</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="106"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="124"/>
       <c r="D1" s="86" t="s">
         <v>1130</v>
       </c>
@@ -5328,14 +5328,14 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="107" t="s">
+    <row r="2" spans="1:30" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="116" t="s">
         <v>1111</v>
       </c>
-      <c r="B2" s="108"/>
-      <c r="C2" s="109"/>
-    </row>
-    <row r="3" spans="1:30" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="117"/>
+      <c r="C2" s="118"/>
+    </row>
+    <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="68" t="s">
         <v>113</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:30" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="66">
         <v>3005</v>
       </c>
@@ -5363,57 +5363,57 @@
       <c r="F4" s="88" t="s">
         <v>1131</v>
       </c>
-      <c r="N4" s="142" t="s">
+      <c r="N4" s="109" t="s">
         <v>1130</v>
       </c>
-      <c r="O4" s="143"/>
-      <c r="P4" s="143"/>
-      <c r="Q4" s="144"/>
-      <c r="U4" s="142" t="s">
+      <c r="O4" s="110"/>
+      <c r="P4" s="110"/>
+      <c r="Q4" s="111"/>
+      <c r="U4" s="109" t="s">
         <v>1144</v>
       </c>
-      <c r="V4" s="143"/>
-      <c r="W4" s="143"/>
-      <c r="X4" s="144"/>
-      <c r="AA4" s="142" t="s">
+      <c r="V4" s="110"/>
+      <c r="W4" s="110"/>
+      <c r="X4" s="111"/>
+      <c r="AA4" s="109" t="s">
         <v>1150</v>
       </c>
-      <c r="AB4" s="143"/>
-      <c r="AC4" s="143"/>
-      <c r="AD4" s="144"/>
-    </row>
-    <row r="5" spans="1:30" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="110" t="s">
+      <c r="AB4" s="110"/>
+      <c r="AC4" s="110"/>
+      <c r="AD4" s="111"/>
+    </row>
+    <row r="5" spans="1:30" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="125" t="s">
         <v>1112</v>
       </c>
-      <c r="B5" s="111"/>
-      <c r="C5" s="112"/>
-      <c r="N5" s="98" t="s">
+      <c r="B5" s="126"/>
+      <c r="C5" s="127"/>
+      <c r="N5" s="99" t="s">
         <v>1110</v>
       </c>
-      <c r="O5" s="99"/>
-      <c r="P5" s="102" t="s">
+      <c r="O5" s="100"/>
+      <c r="P5" s="103" t="s">
         <v>1136</v>
       </c>
-      <c r="Q5" s="99"/>
-      <c r="U5" s="98" t="s">
+      <c r="Q5" s="100"/>
+      <c r="U5" s="99" t="s">
         <v>1110</v>
       </c>
-      <c r="V5" s="99"/>
-      <c r="W5" s="150" t="s">
+      <c r="V5" s="100"/>
+      <c r="W5" s="112" t="s">
         <v>1152</v>
       </c>
-      <c r="X5" s="151"/>
-      <c r="AA5" s="98" t="s">
+      <c r="X5" s="113"/>
+      <c r="AA5" s="99" t="s">
         <v>1110</v>
       </c>
-      <c r="AB5" s="99"/>
-      <c r="AC5" s="102" t="s">
+      <c r="AB5" s="100"/>
+      <c r="AC5" s="103" t="s">
         <v>1155</v>
       </c>
-      <c r="AD5" s="99"/>
-    </row>
-    <row r="6" spans="1:30" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="AD5" s="100"/>
+    </row>
+    <row r="6" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>113</v>
       </c>
@@ -5423,26 +5423,26 @@
       <c r="C6" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="N6" s="100"/>
-      <c r="O6" s="101"/>
-      <c r="P6" s="103">
+      <c r="N6" s="101"/>
+      <c r="O6" s="102"/>
+      <c r="P6" s="104">
         <v>8.9800000000000005E-2</v>
       </c>
-      <c r="Q6" s="101"/>
-      <c r="U6" s="100"/>
-      <c r="V6" s="101"/>
-      <c r="W6" s="148">
+      <c r="Q6" s="102"/>
+      <c r="U6" s="101"/>
+      <c r="V6" s="102"/>
+      <c r="W6" s="114">
         <v>8.9700000000000002E-2</v>
       </c>
-      <c r="X6" s="149"/>
-      <c r="AA6" s="100"/>
-      <c r="AB6" s="101"/>
-      <c r="AC6" s="103">
+      <c r="X6" s="115"/>
+      <c r="AA6" s="101"/>
+      <c r="AB6" s="102"/>
+      <c r="AC6" s="104">
         <v>1.17E-2</v>
       </c>
-      <c r="AD6" s="101"/>
-    </row>
-    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AD6" s="102"/>
+    </row>
+    <row r="7" spans="1:30" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>20002</v>
       </c>
@@ -5452,17 +5452,17 @@
       <c r="C7" s="9" t="s">
         <v>597</v>
       </c>
-      <c r="D7" s="139">
+      <c r="D7" s="121">
         <v>4416</v>
       </c>
-      <c r="E7" s="114" t="s">
+      <c r="E7" s="120" t="s">
         <v>1135</v>
       </c>
-      <c r="F7" s="113" t="s">
+      <c r="F7" s="119" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>20002</v>
       </c>
@@ -5472,11 +5472,11 @@
       <c r="C8" s="9" t="s">
         <v>598</v>
       </c>
-      <c r="D8" s="139"/>
-      <c r="E8" s="114"/>
-      <c r="F8" s="113"/>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="D8" s="121"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="119"/>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>20002</v>
       </c>
@@ -5486,11 +5486,11 @@
       <c r="C9" s="9" t="s">
         <v>599</v>
       </c>
-      <c r="D9" s="139"/>
-      <c r="E9" s="114"/>
-      <c r="F9" s="113"/>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="D9" s="121"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="119"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>20002</v>
       </c>
@@ -5500,11 +5500,11 @@
       <c r="C10" s="9" t="s">
         <v>600</v>
       </c>
-      <c r="D10" s="139"/>
-      <c r="E10" s="114"/>
-      <c r="F10" s="113"/>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="D10" s="121"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="119"/>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>20002</v>
       </c>
@@ -5514,11 +5514,11 @@
       <c r="C11" s="9" t="s">
         <v>601</v>
       </c>
-      <c r="D11" s="139"/>
-      <c r="E11" s="114"/>
-      <c r="F11" s="113"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="D11" s="121"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="119"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>20002</v>
       </c>
@@ -5528,11 +5528,11 @@
       <c r="C12" s="9" t="s">
         <v>602</v>
       </c>
-      <c r="D12" s="139"/>
-      <c r="E12" s="114"/>
-      <c r="F12" s="113"/>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="D12" s="121"/>
+      <c r="E12" s="120"/>
+      <c r="F12" s="119"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>20002</v>
       </c>
@@ -5542,11 +5542,11 @@
       <c r="C13" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="D13" s="139"/>
-      <c r="E13" s="114"/>
-      <c r="F13" s="113"/>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.45">
+      <c r="D13" s="121"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="119"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>20002</v>
       </c>
@@ -5556,11 +5556,11 @@
       <c r="C14" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="D14" s="139"/>
-      <c r="E14" s="114"/>
-      <c r="F14" s="113"/>
-    </row>
-    <row r="15" spans="1:30" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D14" s="121"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="119"/>
+    </row>
+    <row r="15" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <v>20002</v>
       </c>
@@ -5570,18 +5570,18 @@
       <c r="C15" s="14" t="s">
         <v>605</v>
       </c>
-      <c r="D15" s="139"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="113"/>
-    </row>
-    <row r="16" spans="1:30" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="107" t="s">
+      <c r="D15" s="121"/>
+      <c r="E15" s="120"/>
+      <c r="F15" s="119"/>
+    </row>
+    <row r="16" spans="1:30" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="116" t="s">
         <v>1107</v>
       </c>
-      <c r="B16" s="108"/>
-      <c r="C16" s="109"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B16" s="117"/>
+      <c r="C16" s="118"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="61" t="s">
         <v>95</v>
       </c>
@@ -5590,7 +5590,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>606</v>
       </c>
@@ -5604,7 +5604,7 @@
       <c r="E18" s="87"/>
       <c r="F18" s="87"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>608</v>
       </c>
@@ -5618,7 +5618,7 @@
       <c r="E19" s="87"/>
       <c r="F19" s="87"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>610</v>
       </c>
@@ -5632,7 +5632,7 @@
       <c r="E20" s="87"/>
       <c r="F20" s="87"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>612</v>
       </c>
@@ -5646,7 +5646,7 @@
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>614</v>
       </c>
@@ -5660,7 +5660,7 @@
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>616</v>
       </c>
@@ -5674,7 +5674,7 @@
       <c r="E23" s="87"/>
       <c r="F23" s="87"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>618</v>
       </c>
@@ -5688,7 +5688,7 @@
       <c r="E24" s="87"/>
       <c r="F24" s="87"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>620</v>
       </c>
@@ -5702,7 +5702,7 @@
       <c r="E25" s="87"/>
       <c r="F25" s="87"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>622</v>
       </c>
@@ -5716,7 +5716,7 @@
       <c r="E26" s="87"/>
       <c r="F26" s="87"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>624</v>
       </c>
@@ -5730,7 +5730,7 @@
       <c r="E27" s="87"/>
       <c r="F27" s="87"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>626</v>
       </c>
@@ -5744,7 +5744,7 @@
       <c r="E28" s="87"/>
       <c r="F28" s="87"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>628</v>
       </c>
@@ -5758,7 +5758,7 @@
       <c r="E29" s="87"/>
       <c r="F29" s="87"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>630</v>
       </c>
@@ -5772,7 +5772,7 @@
       <c r="E30" s="87"/>
       <c r="F30" s="87"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>632</v>
       </c>
@@ -5786,7 +5786,7 @@
       <c r="E31" s="87"/>
       <c r="F31" s="87"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>634</v>
       </c>
@@ -5800,7 +5800,7 @@
       <c r="E32" s="87"/>
       <c r="F32" s="87"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>636</v>
       </c>
@@ -5814,7 +5814,7 @@
       <c r="E33" s="87"/>
       <c r="F33" s="87"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>638</v>
       </c>
@@ -5828,7 +5828,7 @@
       <c r="E34" s="87"/>
       <c r="F34" s="87"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>640</v>
       </c>
@@ -5842,7 +5842,7 @@
       <c r="E35" s="87"/>
       <c r="F35" s="87"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>642</v>
       </c>
@@ -5856,7 +5856,7 @@
       <c r="E36" s="87"/>
       <c r="F36" s="87"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>644</v>
       </c>
@@ -5870,7 +5870,7 @@
       <c r="E37" s="87"/>
       <c r="F37" s="87"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>646</v>
       </c>
@@ -5884,7 +5884,7 @@
       <c r="E38" s="87"/>
       <c r="F38" s="87"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>648</v>
       </c>
@@ -5898,7 +5898,7 @@
       <c r="E39" s="87"/>
       <c r="F39" s="87"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>650</v>
       </c>
@@ -5912,7 +5912,7 @@
       <c r="E40" s="87"/>
       <c r="F40" s="87"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>652</v>
       </c>
@@ -5926,7 +5926,7 @@
       <c r="E41" s="87"/>
       <c r="F41" s="87"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>654</v>
       </c>
@@ -5940,7 +5940,7 @@
       <c r="E42" s="87"/>
       <c r="F42" s="87"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>656</v>
       </c>
@@ -5954,7 +5954,7 @@
       <c r="E43" s="87"/>
       <c r="F43" s="87"/>
     </row>
-    <row r="44" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>658</v>
       </c>
@@ -5968,14 +5968,14 @@
       <c r="E44" s="87"/>
       <c r="F44" s="87"/>
     </row>
-    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="107" t="s">
+    <row r="45" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="116" t="s">
         <v>1108</v>
       </c>
-      <c r="B45" s="108"/>
-      <c r="C45" s="109"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B45" s="117"/>
+      <c r="C45" s="118"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="24" t="s">
         <v>96</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>660</v>
       </c>
@@ -5998,7 +5998,7 @@
       <c r="E47" s="87"/>
       <c r="F47" s="87"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>662</v>
       </c>
@@ -6012,7 +6012,7 @@
       <c r="E48" s="87"/>
       <c r="F48" s="87"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>664</v>
       </c>
@@ -6026,7 +6026,7 @@
       <c r="E49" s="87"/>
       <c r="F49" s="87"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>666</v>
       </c>
@@ -6040,7 +6040,7 @@
       <c r="E50" s="87"/>
       <c r="F50" s="87"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>668</v>
       </c>
@@ -6054,7 +6054,7 @@
       <c r="E51" s="87"/>
       <c r="F51" s="87"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>670</v>
       </c>
@@ -6068,7 +6068,7 @@
       <c r="E52" s="87"/>
       <c r="F52" s="87"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>672</v>
       </c>
@@ -6082,7 +6082,7 @@
       <c r="E53" s="87"/>
       <c r="F53" s="87"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>674</v>
       </c>
@@ -6096,7 +6096,7 @@
       <c r="E54" s="87"/>
       <c r="F54" s="87"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>676</v>
       </c>
@@ -6110,7 +6110,7 @@
       <c r="E55" s="87"/>
       <c r="F55" s="87"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>678</v>
       </c>
@@ -6124,7 +6124,7 @@
       <c r="E56" s="87"/>
       <c r="F56" s="87"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>680</v>
       </c>
@@ -6138,7 +6138,7 @@
       <c r="E57" s="87"/>
       <c r="F57" s="87"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>682</v>
       </c>
@@ -6152,7 +6152,7 @@
       <c r="E58" s="87"/>
       <c r="F58" s="87"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>684</v>
       </c>
@@ -6166,7 +6166,7 @@
       <c r="E59" s="87"/>
       <c r="F59" s="87"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>686</v>
       </c>
@@ -6180,7 +6180,7 @@
       <c r="E60" s="87"/>
       <c r="F60" s="87"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>688</v>
       </c>
@@ -6194,7 +6194,7 @@
       <c r="E61" s="87"/>
       <c r="F61" s="87"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>690</v>
       </c>
@@ -6208,7 +6208,7 @@
       <c r="E62" s="87"/>
       <c r="F62" s="87"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>692</v>
       </c>
@@ -6222,7 +6222,7 @@
       <c r="E63" s="87"/>
       <c r="F63" s="87"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>694</v>
       </c>
@@ -6236,7 +6236,7 @@
       <c r="E64" s="87"/>
       <c r="F64" s="87"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>696</v>
       </c>
@@ -6250,7 +6250,7 @@
       <c r="E65" s="87"/>
       <c r="F65" s="87"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>698</v>
       </c>
@@ -6264,7 +6264,7 @@
       <c r="E66" s="87"/>
       <c r="F66" s="87"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>700</v>
       </c>
@@ -6278,7 +6278,7 @@
       <c r="E67" s="87"/>
       <c r="F67" s="87"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>702</v>
       </c>
@@ -6292,7 +6292,7 @@
       <c r="E68" s="87"/>
       <c r="F68" s="87"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
         <v>704</v>
       </c>
@@ -6306,7 +6306,7 @@
       <c r="E69" s="87"/>
       <c r="F69" s="87"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
         <v>706</v>
       </c>
@@ -6320,7 +6320,7 @@
       <c r="E70" s="87"/>
       <c r="F70" s="87"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
         <v>708</v>
       </c>
@@ -6334,7 +6334,7 @@
       <c r="E71" s="87"/>
       <c r="F71" s="87"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
         <v>710</v>
       </c>
@@ -6348,7 +6348,7 @@
       <c r="E72" s="87"/>
       <c r="F72" s="87"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>712</v>
       </c>
@@ -6362,7 +6362,7 @@
       <c r="E73" s="87"/>
       <c r="F73" s="87"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>714</v>
       </c>
@@ -6376,7 +6376,7 @@
       <c r="E74" s="87"/>
       <c r="F74" s="87"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
         <v>716</v>
       </c>
@@ -6390,7 +6390,7 @@
       <c r="E75" s="87"/>
       <c r="F75" s="87"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
         <v>718</v>
       </c>
@@ -6404,7 +6404,7 @@
       <c r="E76" s="87"/>
       <c r="F76" s="87"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>720</v>
       </c>
@@ -6418,7 +6418,7 @@
       <c r="E77" s="87"/>
       <c r="F77" s="87"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>722</v>
       </c>
@@ -6432,7 +6432,7 @@
       <c r="E78" s="87"/>
       <c r="F78" s="87"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>723</v>
       </c>
@@ -6446,7 +6446,7 @@
       <c r="E79" s="87"/>
       <c r="F79" s="87"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
         <v>725</v>
       </c>
@@ -6460,7 +6460,7 @@
       <c r="E80" s="87"/>
       <c r="F80" s="87"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
         <v>727</v>
       </c>
@@ -6474,7 +6474,7 @@
       <c r="E81" s="87"/>
       <c r="F81" s="87"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
         <v>729</v>
       </c>
@@ -6488,7 +6488,7 @@
       <c r="E82" s="87"/>
       <c r="F82" s="87"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>731</v>
       </c>
@@ -6502,7 +6502,7 @@
       <c r="E83" s="87"/>
       <c r="F83" s="87"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>733</v>
       </c>
@@ -6516,7 +6516,7 @@
       <c r="E84" s="87"/>
       <c r="F84" s="87"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>735</v>
       </c>
@@ -6530,7 +6530,7 @@
       <c r="E85" s="87"/>
       <c r="F85" s="87"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
         <v>737</v>
       </c>
@@ -6544,7 +6544,7 @@
       <c r="E86" s="87"/>
       <c r="F86" s="87"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
         <v>739</v>
       </c>
@@ -6558,7 +6558,7 @@
       <c r="E87" s="87"/>
       <c r="F87" s="87"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
         <v>741</v>
       </c>
@@ -6572,7 +6572,7 @@
       <c r="E88" s="87"/>
       <c r="F88" s="87"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
         <v>743</v>
       </c>
@@ -6586,7 +6586,7 @@
       <c r="E89" s="87"/>
       <c r="F89" s="87"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
         <v>745</v>
       </c>
@@ -6600,7 +6600,7 @@
       <c r="E90" s="87"/>
       <c r="F90" s="87"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>747</v>
       </c>
@@ -6614,7 +6614,7 @@
       <c r="E91" s="87"/>
       <c r="F91" s="87"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
         <v>749</v>
       </c>
@@ -6628,7 +6628,7 @@
       <c r="E92" s="87"/>
       <c r="F92" s="87"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
         <v>751</v>
       </c>
@@ -6642,7 +6642,7 @@
       <c r="E93" s="87"/>
       <c r="F93" s="87"/>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>753</v>
       </c>
@@ -6656,7 +6656,7 @@
       <c r="E94" s="87"/>
       <c r="F94" s="87"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
         <v>755</v>
       </c>
@@ -6670,7 +6670,7 @@
       <c r="E95" s="87"/>
       <c r="F95" s="87"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
         <v>757</v>
       </c>
@@ -6684,7 +6684,7 @@
       <c r="E96" s="87"/>
       <c r="F96" s="87"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
         <v>759</v>
       </c>
@@ -6698,7 +6698,7 @@
       <c r="E97" s="87"/>
       <c r="F97" s="87"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
         <v>761</v>
       </c>
@@ -6712,7 +6712,7 @@
       <c r="E98" s="87"/>
       <c r="F98" s="87"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
         <v>763</v>
       </c>
@@ -6726,7 +6726,7 @@
       <c r="E99" s="87"/>
       <c r="F99" s="87"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
         <v>765</v>
       </c>
@@ -6740,7 +6740,7 @@
       <c r="E100" s="87"/>
       <c r="F100" s="87"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
         <v>767</v>
       </c>
@@ -6754,7 +6754,7 @@
       <c r="E101" s="87"/>
       <c r="F101" s="87"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
         <v>769</v>
       </c>
@@ -6768,7 +6768,7 @@
       <c r="E102" s="87"/>
       <c r="F102" s="87"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
         <v>771</v>
       </c>
@@ -6782,7 +6782,7 @@
       <c r="E103" s="87"/>
       <c r="F103" s="87"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
         <v>773</v>
       </c>
@@ -6796,7 +6796,7 @@
       <c r="E104" s="87"/>
       <c r="F104" s="87"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
         <v>775</v>
       </c>
@@ -6810,7 +6810,7 @@
       <c r="E105" s="87"/>
       <c r="F105" s="87"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
         <v>776</v>
       </c>
@@ -6824,7 +6824,7 @@
       <c r="E106" s="87"/>
       <c r="F106" s="87"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
         <v>778</v>
       </c>
@@ -6838,7 +6838,7 @@
       <c r="E107" s="87"/>
       <c r="F107" s="87"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
         <v>780</v>
       </c>
@@ -6852,7 +6852,7 @@
       <c r="E108" s="87"/>
       <c r="F108" s="87"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
         <v>782</v>
       </c>
@@ -6866,7 +6866,7 @@
       <c r="E109" s="87"/>
       <c r="F109" s="87"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
         <v>784</v>
       </c>
@@ -6880,7 +6880,7 @@
       <c r="E110" s="87"/>
       <c r="F110" s="87"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
         <v>786</v>
       </c>
@@ -6894,7 +6894,7 @@
       <c r="E111" s="87"/>
       <c r="F111" s="87"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
         <v>788</v>
       </c>
@@ -6908,7 +6908,7 @@
       <c r="E112" s="87"/>
       <c r="F112" s="87"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
         <v>790</v>
       </c>
@@ -6922,7 +6922,7 @@
       <c r="E113" s="87"/>
       <c r="F113" s="87"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
         <v>792</v>
       </c>
@@ -6936,7 +6936,7 @@
       <c r="E114" s="87"/>
       <c r="F114" s="87"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
         <v>794</v>
       </c>
@@ -6950,7 +6950,7 @@
       <c r="E115" s="87"/>
       <c r="F115" s="87"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
         <v>796</v>
       </c>
@@ -6964,7 +6964,7 @@
       <c r="E116" s="87"/>
       <c r="F116" s="87"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
         <v>798</v>
       </c>
@@ -6978,7 +6978,7 @@
       <c r="E117" s="87"/>
       <c r="F117" s="87"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
         <v>800</v>
       </c>
@@ -6992,7 +6992,7 @@
       <c r="E118" s="87"/>
       <c r="F118" s="87"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
         <v>802</v>
       </c>
@@ -7006,7 +7006,7 @@
       <c r="E119" s="87"/>
       <c r="F119" s="87"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
         <v>804</v>
       </c>
@@ -7020,7 +7020,7 @@
       <c r="E120" s="87"/>
       <c r="F120" s="87"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
         <v>806</v>
       </c>
@@ -7034,7 +7034,7 @@
       <c r="E121" s="87"/>
       <c r="F121" s="87"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
         <v>808</v>
       </c>
@@ -7048,7 +7048,7 @@
       <c r="E122" s="87"/>
       <c r="F122" s="87"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
         <v>810</v>
       </c>
@@ -7062,7 +7062,7 @@
       <c r="E123" s="87"/>
       <c r="F123" s="87"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
         <v>812</v>
       </c>
@@ -7076,7 +7076,7 @@
       <c r="E124" s="87"/>
       <c r="F124" s="87"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
         <v>814</v>
       </c>
@@ -7090,7 +7090,7 @@
       <c r="E125" s="87"/>
       <c r="F125" s="87"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
         <v>816</v>
       </c>
@@ -7104,7 +7104,7 @@
       <c r="E126" s="87"/>
       <c r="F126" s="87"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
         <v>818</v>
       </c>
@@ -7118,7 +7118,7 @@
       <c r="E127" s="87"/>
       <c r="F127" s="87"/>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
         <v>820</v>
       </c>
@@ -7132,7 +7132,7 @@
       <c r="E128" s="87"/>
       <c r="F128" s="87"/>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
         <v>822</v>
       </c>
@@ -7146,7 +7146,7 @@
       <c r="E129" s="87"/>
       <c r="F129" s="87"/>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
         <v>824</v>
       </c>
@@ -7160,7 +7160,7 @@
       <c r="E130" s="87"/>
       <c r="F130" s="87"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
         <v>826</v>
       </c>
@@ -7174,7 +7174,7 @@
       <c r="E131" s="87"/>
       <c r="F131" s="87"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
         <v>828</v>
       </c>
@@ -7188,7 +7188,7 @@
       <c r="E132" s="87"/>
       <c r="F132" s="87"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
         <v>830</v>
       </c>
@@ -7202,7 +7202,7 @@
       <c r="E133" s="87"/>
       <c r="F133" s="87"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
         <v>831</v>
       </c>
@@ -7216,7 +7216,7 @@
       <c r="E134" s="87"/>
       <c r="F134" s="87"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
         <v>833</v>
       </c>
@@ -7230,7 +7230,7 @@
       <c r="E135" s="87"/>
       <c r="F135" s="87"/>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
         <v>835</v>
       </c>
@@ -7244,7 +7244,7 @@
       <c r="E136" s="87"/>
       <c r="F136" s="87"/>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
         <v>837</v>
       </c>
@@ -7258,7 +7258,7 @@
       <c r="E137" s="87"/>
       <c r="F137" s="87"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
         <v>839</v>
       </c>
@@ -7272,7 +7272,7 @@
       <c r="E138" s="87"/>
       <c r="F138" s="87"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
         <v>841</v>
       </c>
@@ -7286,7 +7286,7 @@
       <c r="E139" s="87"/>
       <c r="F139" s="87"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
         <v>843</v>
       </c>
@@ -7300,7 +7300,7 @@
       <c r="E140" s="87"/>
       <c r="F140" s="87"/>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
         <v>845</v>
       </c>
@@ -7314,7 +7314,7 @@
       <c r="E141" s="87"/>
       <c r="F141" s="87"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
         <v>847</v>
       </c>
@@ -7328,7 +7328,7 @@
       <c r="E142" s="87"/>
       <c r="F142" s="87"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
         <v>849</v>
       </c>
@@ -7342,7 +7342,7 @@
       <c r="E143" s="87"/>
       <c r="F143" s="87"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
         <v>851</v>
       </c>
@@ -7356,7 +7356,7 @@
       <c r="E144" s="87"/>
       <c r="F144" s="87"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
         <v>853</v>
       </c>
@@ -7370,7 +7370,7 @@
       <c r="E145" s="87"/>
       <c r="F145" s="87"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
         <v>855</v>
       </c>
@@ -7384,7 +7384,7 @@
       <c r="E146" s="87"/>
       <c r="F146" s="87"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
         <v>857</v>
       </c>
@@ -7398,7 +7398,7 @@
       <c r="E147" s="87"/>
       <c r="F147" s="87"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
         <v>859</v>
       </c>
@@ -7412,7 +7412,7 @@
       <c r="E148" s="87"/>
       <c r="F148" s="87"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
         <v>861</v>
       </c>
@@ -7426,7 +7426,7 @@
       <c r="E149" s="87"/>
       <c r="F149" s="87"/>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
         <v>863</v>
       </c>
@@ -7440,7 +7440,7 @@
       <c r="E150" s="87"/>
       <c r="F150" s="87"/>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
         <v>865</v>
       </c>
@@ -7454,7 +7454,7 @@
       <c r="E151" s="87"/>
       <c r="F151" s="87"/>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
         <v>867</v>
       </c>
@@ -7468,7 +7468,7 @@
       <c r="E152" s="87"/>
       <c r="F152" s="87"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
         <v>869</v>
       </c>
@@ -7482,7 +7482,7 @@
       <c r="E153" s="87"/>
       <c r="F153" s="87"/>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
         <v>871</v>
       </c>
@@ -7496,7 +7496,7 @@
       <c r="E154" s="87"/>
       <c r="F154" s="87"/>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
         <v>873</v>
       </c>
@@ -7510,7 +7510,7 @@
       <c r="E155" s="87"/>
       <c r="F155" s="87"/>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
         <v>875</v>
       </c>
@@ -7524,7 +7524,7 @@
       <c r="E156" s="87"/>
       <c r="F156" s="87"/>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
         <v>877</v>
       </c>
@@ -7538,7 +7538,7 @@
       <c r="E157" s="87"/>
       <c r="F157" s="87"/>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
         <v>879</v>
       </c>
@@ -7552,7 +7552,7 @@
       <c r="E158" s="87"/>
       <c r="F158" s="87"/>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
         <v>881</v>
       </c>
@@ -7566,7 +7566,7 @@
       <c r="E159" s="87"/>
       <c r="F159" s="87"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
         <v>883</v>
       </c>
@@ -7580,7 +7580,7 @@
       <c r="E160" s="87"/>
       <c r="F160" s="87"/>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
         <v>885</v>
       </c>
@@ -7594,7 +7594,7 @@
       <c r="E161" s="87"/>
       <c r="F161" s="87"/>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
         <v>887</v>
       </c>
@@ -7608,7 +7608,7 @@
       <c r="E162" s="87"/>
       <c r="F162" s="87"/>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
         <v>889</v>
       </c>
@@ -7622,7 +7622,7 @@
       <c r="E163" s="87"/>
       <c r="F163" s="87"/>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
         <v>891</v>
       </c>
@@ -7636,7 +7636,7 @@
       <c r="E164" s="87"/>
       <c r="F164" s="87"/>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
         <v>893</v>
       </c>
@@ -7650,7 +7650,7 @@
       <c r="E165" s="87"/>
       <c r="F165" s="87"/>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
         <v>895</v>
       </c>
@@ -7664,7 +7664,7 @@
       <c r="E166" s="87"/>
       <c r="F166" s="87"/>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
         <v>897</v>
       </c>
@@ -7678,7 +7678,7 @@
       <c r="E167" s="87"/>
       <c r="F167" s="87"/>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
         <v>899</v>
       </c>
@@ -7692,7 +7692,7 @@
       <c r="E168" s="87"/>
       <c r="F168" s="87"/>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
         <v>901</v>
       </c>
@@ -7706,7 +7706,7 @@
       <c r="E169" s="87"/>
       <c r="F169" s="87"/>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
         <v>903</v>
       </c>
@@ -7720,7 +7720,7 @@
       <c r="E170" s="87"/>
       <c r="F170" s="87"/>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
         <v>905</v>
       </c>
@@ -7734,7 +7734,7 @@
       <c r="E171" s="87"/>
       <c r="F171" s="87"/>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
         <v>907</v>
       </c>
@@ -7748,7 +7748,7 @@
       <c r="E172" s="87"/>
       <c r="F172" s="87"/>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
         <v>909</v>
       </c>
@@ -7762,7 +7762,7 @@
       <c r="E173" s="87"/>
       <c r="F173" s="87"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
         <v>911</v>
       </c>
@@ -7776,7 +7776,7 @@
       <c r="E174" s="87"/>
       <c r="F174" s="87"/>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
         <v>913</v>
       </c>
@@ -7790,7 +7790,7 @@
       <c r="E175" s="87"/>
       <c r="F175" s="87"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
         <v>915</v>
       </c>
@@ -7804,7 +7804,7 @@
       <c r="E176" s="87"/>
       <c r="F176" s="87"/>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
         <v>917</v>
       </c>
@@ -7818,7 +7818,7 @@
       <c r="E177" s="87"/>
       <c r="F177" s="87"/>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
         <v>919</v>
       </c>
@@ -7832,7 +7832,7 @@
       <c r="E178" s="87"/>
       <c r="F178" s="87"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
         <v>921</v>
       </c>
@@ -7846,7 +7846,7 @@
       <c r="E179" s="87"/>
       <c r="F179" s="87"/>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
         <v>923</v>
       </c>
@@ -7860,7 +7860,7 @@
       <c r="E180" s="87"/>
       <c r="F180" s="87"/>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>925</v>
       </c>
@@ -7874,7 +7874,7 @@
       <c r="E181" s="87"/>
       <c r="F181" s="87"/>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
         <v>927</v>
       </c>
@@ -7888,7 +7888,7 @@
       <c r="E182" s="87"/>
       <c r="F182" s="87"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
         <v>929</v>
       </c>
@@ -7902,7 +7902,7 @@
       <c r="E183" s="87"/>
       <c r="F183" s="87"/>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
         <v>931</v>
       </c>
@@ -7916,7 +7916,7 @@
       <c r="E184" s="87"/>
       <c r="F184" s="87"/>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
         <v>933</v>
       </c>
@@ -7930,7 +7930,7 @@
       <c r="E185" s="87"/>
       <c r="F185" s="87"/>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
         <v>935</v>
       </c>
@@ -7944,7 +7944,7 @@
       <c r="E186" s="87"/>
       <c r="F186" s="87"/>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
         <v>937</v>
       </c>
@@ -7958,7 +7958,7 @@
       <c r="E187" s="87"/>
       <c r="F187" s="87"/>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
         <v>939</v>
       </c>
@@ -7972,7 +7972,7 @@
       <c r="E188" s="87"/>
       <c r="F188" s="87"/>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
         <v>941</v>
       </c>
@@ -7986,7 +7986,7 @@
       <c r="E189" s="87"/>
       <c r="F189" s="87"/>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
         <v>943</v>
       </c>
@@ -8000,7 +8000,7 @@
       <c r="E190" s="87"/>
       <c r="F190" s="87"/>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
         <v>945</v>
       </c>
@@ -8014,7 +8014,7 @@
       <c r="E191" s="87"/>
       <c r="F191" s="87"/>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
         <v>947</v>
       </c>
@@ -8028,7 +8028,7 @@
       <c r="E192" s="87"/>
       <c r="F192" s="87"/>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
         <v>949</v>
       </c>
@@ -8042,7 +8042,7 @@
       <c r="E193" s="87"/>
       <c r="F193" s="87"/>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
         <v>950</v>
       </c>
@@ -8056,7 +8056,7 @@
       <c r="E194" s="87"/>
       <c r="F194" s="87"/>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
         <v>951</v>
       </c>
@@ -8070,7 +8070,7 @@
       <c r="E195" s="87"/>
       <c r="F195" s="87"/>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
         <v>953</v>
       </c>
@@ -8084,7 +8084,7 @@
       <c r="E196" s="87"/>
       <c r="F196" s="87"/>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
         <v>955</v>
       </c>
@@ -8098,7 +8098,7 @@
       <c r="E197" s="87"/>
       <c r="F197" s="87"/>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
         <v>957</v>
       </c>
@@ -8112,7 +8112,7 @@
       <c r="E198" s="87"/>
       <c r="F198" s="87"/>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
         <v>959</v>
       </c>
@@ -8126,7 +8126,7 @@
       <c r="E199" s="87"/>
       <c r="F199" s="87"/>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>961</v>
       </c>
@@ -8140,7 +8140,7 @@
       <c r="E200" s="87"/>
       <c r="F200" s="87"/>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>963</v>
       </c>
@@ -8154,7 +8154,7 @@
       <c r="E201" s="87"/>
       <c r="F201" s="87"/>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>965</v>
       </c>
@@ -8168,7 +8168,7 @@
       <c r="E202" s="87"/>
       <c r="F202" s="87"/>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
         <v>967</v>
       </c>
@@ -8182,7 +8182,7 @@
       <c r="E203" s="87"/>
       <c r="F203" s="87"/>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
         <v>969</v>
       </c>
@@ -8196,7 +8196,7 @@
       <c r="E204" s="87"/>
       <c r="F204" s="87"/>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
         <v>971</v>
       </c>
@@ -8210,7 +8210,7 @@
       <c r="E205" s="87"/>
       <c r="F205" s="87"/>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
         <v>973</v>
       </c>
@@ -8224,7 +8224,7 @@
       <c r="E206" s="87"/>
       <c r="F206" s="87"/>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
         <v>975</v>
       </c>
@@ -8238,7 +8238,7 @@
       <c r="E207" s="87"/>
       <c r="F207" s="87"/>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
         <v>977</v>
       </c>
@@ -8252,7 +8252,7 @@
       <c r="E208" s="87"/>
       <c r="F208" s="87"/>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
         <v>979</v>
       </c>
@@ -8266,7 +8266,7 @@
       <c r="E209" s="87"/>
       <c r="F209" s="87"/>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="7" t="s">
         <v>981</v>
       </c>
@@ -8280,7 +8280,7 @@
       <c r="E210" s="87"/>
       <c r="F210" s="87"/>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
         <v>983</v>
       </c>
@@ -8294,7 +8294,7 @@
       <c r="E211" s="87"/>
       <c r="F211" s="87"/>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="7" t="s">
         <v>985</v>
       </c>
@@ -8308,7 +8308,7 @@
       <c r="E212" s="87"/>
       <c r="F212" s="87"/>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="7" t="s">
         <v>987</v>
       </c>
@@ -8322,7 +8322,7 @@
       <c r="E213" s="87"/>
       <c r="F213" s="87"/>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="7" t="s">
         <v>989</v>
       </c>
@@ -8336,7 +8336,7 @@
       <c r="E214" s="87"/>
       <c r="F214" s="87"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
         <v>991</v>
       </c>
@@ -8350,7 +8350,7 @@
       <c r="E215" s="87"/>
       <c r="F215" s="87"/>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="7" t="s">
         <v>993</v>
       </c>
@@ -8364,7 +8364,7 @@
       <c r="E216" s="87"/>
       <c r="F216" s="87"/>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
         <v>995</v>
       </c>
@@ -8378,7 +8378,7 @@
       <c r="E217" s="87"/>
       <c r="F217" s="87"/>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="7" t="s">
         <v>997</v>
       </c>
@@ -8392,7 +8392,7 @@
       <c r="E218" s="87"/>
       <c r="F218" s="87"/>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
         <v>999</v>
       </c>
@@ -8406,7 +8406,7 @@
       <c r="E219" s="87"/>
       <c r="F219" s="87"/>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="7" t="s">
         <v>1001</v>
       </c>
@@ -8420,7 +8420,7 @@
       <c r="E220" s="87"/>
       <c r="F220" s="87"/>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
         <v>1003</v>
       </c>
@@ -8434,7 +8434,7 @@
       <c r="E221" s="87"/>
       <c r="F221" s="87"/>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="7" t="s">
         <v>1005</v>
       </c>
@@ -8448,7 +8448,7 @@
       <c r="E222" s="87"/>
       <c r="F222" s="87"/>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
         <v>1007</v>
       </c>
@@ -8462,7 +8462,7 @@
       <c r="E223" s="87"/>
       <c r="F223" s="87"/>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="7" t="s">
         <v>1009</v>
       </c>
@@ -8476,7 +8476,7 @@
       <c r="E224" s="87"/>
       <c r="F224" s="87"/>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="7" t="s">
         <v>1011</v>
       </c>
@@ -8490,7 +8490,7 @@
       <c r="E225" s="87"/>
       <c r="F225" s="87"/>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="7" t="s">
         <v>1013</v>
       </c>
@@ -8504,7 +8504,7 @@
       <c r="E226" s="87"/>
       <c r="F226" s="87"/>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="7" t="s">
         <v>1015</v>
       </c>
@@ -8518,7 +8518,7 @@
       <c r="E227" s="87"/>
       <c r="F227" s="87"/>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="7" t="s">
         <v>1017</v>
       </c>
@@ -8532,7 +8532,7 @@
       <c r="E228" s="87"/>
       <c r="F228" s="87"/>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="7" t="s">
         <v>1019</v>
       </c>
@@ -8546,7 +8546,7 @@
       <c r="E229" s="87"/>
       <c r="F229" s="87"/>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="7" t="s">
         <v>1021</v>
       </c>
@@ -8560,7 +8560,7 @@
       <c r="E230" s="87"/>
       <c r="F230" s="87"/>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="7" t="s">
         <v>1023</v>
       </c>
@@ -8574,7 +8574,7 @@
       <c r="E231" s="87"/>
       <c r="F231" s="87"/>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="7" t="s">
         <v>1025</v>
       </c>
@@ -8588,7 +8588,7 @@
       <c r="E232" s="87"/>
       <c r="F232" s="87"/>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="7" t="s">
         <v>1027</v>
       </c>
@@ -8602,7 +8602,7 @@
       <c r="E233" s="87"/>
       <c r="F233" s="87"/>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="7" t="s">
         <v>1029</v>
       </c>
@@ -8616,7 +8616,7 @@
       <c r="E234" s="87"/>
       <c r="F234" s="87"/>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="7" t="s">
         <v>1031</v>
       </c>
@@ -8630,7 +8630,7 @@
       <c r="E235" s="87"/>
       <c r="F235" s="87"/>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="7" t="s">
         <v>1033</v>
       </c>
@@ -8644,7 +8644,7 @@
       <c r="E236" s="87"/>
       <c r="F236" s="87"/>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="7" t="s">
         <v>1034</v>
       </c>
@@ -8658,7 +8658,7 @@
       <c r="E237" s="87"/>
       <c r="F237" s="87"/>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="7" t="s">
         <v>1035</v>
       </c>
@@ -8672,7 +8672,7 @@
       <c r="E238" s="87"/>
       <c r="F238" s="87"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="7" t="s">
         <v>1036</v>
       </c>
@@ -8686,7 +8686,7 @@
       <c r="E239" s="87"/>
       <c r="F239" s="87"/>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="7" t="s">
         <v>1037</v>
       </c>
@@ -8700,7 +8700,7 @@
       <c r="E240" s="87"/>
       <c r="F240" s="87"/>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="7" t="s">
         <v>1038</v>
       </c>
@@ -8714,7 +8714,7 @@
       <c r="E241" s="87"/>
       <c r="F241" s="87"/>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="7" t="s">
         <v>1039</v>
       </c>
@@ -8728,7 +8728,7 @@
       <c r="E242" s="87"/>
       <c r="F242" s="87"/>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="7" t="s">
         <v>1041</v>
       </c>
@@ -8742,7 +8742,7 @@
       <c r="E243" s="87"/>
       <c r="F243" s="87"/>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="7" t="s">
         <v>1042</v>
       </c>
@@ -8756,7 +8756,7 @@
       <c r="E244" s="87"/>
       <c r="F244" s="87"/>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="7" t="s">
         <v>1044</v>
       </c>
@@ -8770,7 +8770,7 @@
       <c r="E245" s="87"/>
       <c r="F245" s="87"/>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="7" t="s">
         <v>1045</v>
       </c>
@@ -8784,7 +8784,7 @@
       <c r="E246" s="87"/>
       <c r="F246" s="87"/>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="7" t="s">
         <v>1047</v>
       </c>
@@ -8798,7 +8798,7 @@
       <c r="E247" s="87"/>
       <c r="F247" s="87"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="7" t="s">
         <v>1049</v>
       </c>
@@ -8812,7 +8812,7 @@
       <c r="E248" s="87"/>
       <c r="F248" s="87"/>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="7" t="s">
         <v>1051</v>
       </c>
@@ -8826,7 +8826,7 @@
       <c r="E249" s="87"/>
       <c r="F249" s="87"/>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="7" t="s">
         <v>1052</v>
       </c>
@@ -8840,7 +8840,7 @@
       <c r="E250" s="87"/>
       <c r="F250" s="87"/>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="7" t="s">
         <v>1053</v>
       </c>
@@ -8854,7 +8854,7 @@
       <c r="E251" s="87"/>
       <c r="F251" s="87"/>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="7" t="s">
         <v>1055</v>
       </c>
@@ -8868,7 +8868,7 @@
       <c r="E252" s="87"/>
       <c r="F252" s="87"/>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="7" t="s">
         <v>1057</v>
       </c>
@@ -8882,7 +8882,7 @@
       <c r="E253" s="87"/>
       <c r="F253" s="87"/>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="7" t="s">
         <v>1059</v>
       </c>
@@ -8896,7 +8896,7 @@
       <c r="E254" s="87"/>
       <c r="F254" s="87"/>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="7" t="s">
         <v>1061</v>
       </c>
@@ -8910,7 +8910,7 @@
       <c r="E255" s="87"/>
       <c r="F255" s="87"/>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="7" t="s">
         <v>1063</v>
       </c>
@@ -8924,7 +8924,7 @@
       <c r="E256" s="87"/>
       <c r="F256" s="87"/>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="7" t="s">
         <v>1064</v>
       </c>
@@ -8938,7 +8938,7 @@
       <c r="E257" s="87"/>
       <c r="F257" s="87"/>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="7" t="s">
         <v>1065</v>
       </c>
@@ -8952,7 +8952,7 @@
       <c r="E258" s="87"/>
       <c r="F258" s="87"/>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="7" t="s">
         <v>1066</v>
       </c>
@@ -8966,7 +8966,7 @@
       <c r="E259" s="87"/>
       <c r="F259" s="87"/>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="7" t="s">
         <v>1067</v>
       </c>
@@ -8980,7 +8980,7 @@
       <c r="E260" s="87"/>
       <c r="F260" s="87"/>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="7" t="s">
         <v>1068</v>
       </c>
@@ -8994,7 +8994,7 @@
       <c r="E261" s="87"/>
       <c r="F261" s="87"/>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="7" t="s">
         <v>1070</v>
       </c>
@@ -9008,7 +9008,7 @@
       <c r="E262" s="87"/>
       <c r="F262" s="87"/>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="7" t="s">
         <v>1072</v>
       </c>
@@ -9022,7 +9022,7 @@
       <c r="E263" s="87"/>
       <c r="F263" s="87"/>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="7" t="s">
         <v>1074</v>
       </c>
@@ -9036,7 +9036,7 @@
       <c r="E264" s="87"/>
       <c r="F264" s="87"/>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="7" t="s">
         <v>1076</v>
       </c>
@@ -9050,7 +9050,7 @@
       <c r="E265" s="87"/>
       <c r="F265" s="87"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="7" t="s">
         <v>1077</v>
       </c>
@@ -9064,7 +9064,7 @@
       <c r="E266" s="87"/>
       <c r="F266" s="87"/>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="7" t="s">
         <v>1079</v>
       </c>
@@ -9078,7 +9078,7 @@
       <c r="E267" s="87"/>
       <c r="F267" s="87"/>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="7" t="s">
         <v>1081</v>
       </c>
@@ -9092,7 +9092,7 @@
       <c r="E268" s="87"/>
       <c r="F268" s="87"/>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="7" t="s">
         <v>1083</v>
       </c>
@@ -9106,7 +9106,7 @@
       <c r="E269" s="87"/>
       <c r="F269" s="87"/>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="7" t="s">
         <v>1085</v>
       </c>
@@ -9120,7 +9120,7 @@
       <c r="E270" s="87"/>
       <c r="F270" s="87"/>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="7" t="s">
         <v>1005</v>
       </c>
@@ -9134,7 +9134,7 @@
       <c r="E271" s="87"/>
       <c r="F271" s="87"/>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="7" t="s">
         <v>1017</v>
       </c>
@@ -9148,7 +9148,7 @@
       <c r="E272" s="87"/>
       <c r="F272" s="87"/>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="7" t="s">
         <v>1087</v>
       </c>
@@ -9162,7 +9162,7 @@
       <c r="E273" s="87"/>
       <c r="F273" s="87"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="7" t="s">
         <v>1089</v>
       </c>
@@ -9176,7 +9176,7 @@
       <c r="E274" s="87"/>
       <c r="F274" s="87"/>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="7" t="s">
         <v>1091</v>
       </c>
@@ -9190,7 +9190,7 @@
       <c r="E275" s="87"/>
       <c r="F275" s="87"/>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="7" t="s">
         <v>1093</v>
       </c>
@@ -9204,7 +9204,7 @@
       <c r="E276" s="87"/>
       <c r="F276" s="87"/>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="7" t="s">
         <v>1095</v>
       </c>
@@ -9218,7 +9218,7 @@
       <c r="E277" s="87"/>
       <c r="F277" s="87"/>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="7" t="s">
         <v>1097</v>
       </c>
@@ -9232,7 +9232,7 @@
       <c r="E278" s="87"/>
       <c r="F278" s="87"/>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="7" t="s">
         <v>1099</v>
       </c>
@@ -9246,7 +9246,7 @@
       <c r="E279" s="87"/>
       <c r="F279" s="87"/>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="7" t="s">
         <v>1101</v>
       </c>
@@ -9260,7 +9260,7 @@
       <c r="E280" s="87"/>
       <c r="F280" s="87"/>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="7" t="s">
         <v>1103</v>
       </c>
@@ -9274,7 +9274,7 @@
       <c r="E281" s="87"/>
       <c r="F281" s="87"/>
     </row>
-    <row r="282" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="282" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="11" t="s">
         <v>1105</v>
       </c>
@@ -9290,6 +9290,18 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="N5:O6"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="F7:F15"/>
+    <mergeCell ref="E7:E15"/>
+    <mergeCell ref="D7:D15"/>
     <mergeCell ref="U4:X4"/>
     <mergeCell ref="U5:V6"/>
     <mergeCell ref="W5:X5"/>
@@ -9298,18 +9310,6 @@
     <mergeCell ref="AA5:AB6"/>
     <mergeCell ref="AC5:AD5"/>
     <mergeCell ref="AC6:AD6"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="F7:F15"/>
-    <mergeCell ref="E7:E15"/>
-    <mergeCell ref="D7:D15"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="N5:O6"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="N4:Q4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9320,17 +9320,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{485799B7-C756-451B-84C8-6DF85725E8BA}">
   <dimension ref="A1:AA68"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="101.73046875" customWidth="1"/>
+    <col min="3" max="3" width="101.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="117" t="s">
+    <row r="1" spans="1:27" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="133" t="s">
         <v>1114</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="119"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="135"/>
       <c r="D1" s="86" t="s">
         <v>1130</v>
       </c>
@@ -9344,12 +9344,12 @@
       <c r="N1" s="71"/>
       <c r="O1" s="71"/>
     </row>
-    <row r="2" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="107" t="s">
+    <row r="2" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="116" t="s">
         <v>1113</v>
       </c>
-      <c r="B2" s="108"/>
-      <c r="C2" s="109"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="118"/>
       <c r="H2" s="72"/>
       <c r="I2" s="72"/>
       <c r="J2" s="74"/>
@@ -9358,7 +9358,7 @@
       <c r="N2" s="71"/>
       <c r="O2" s="71"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>113</v>
       </c>
@@ -9379,7 +9379,7 @@
       <c r="N3" s="71"/>
       <c r="O3" s="71"/>
     </row>
-    <row r="4" spans="1:27" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>20002</v>
       </c>
@@ -9406,12 +9406,12 @@
       <c r="N4" s="71"/>
       <c r="O4" s="71"/>
     </row>
-    <row r="5" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="107" t="s">
+    <row r="5" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="116" t="s">
         <v>1107</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="109"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="118"/>
       <c r="H5" s="72"/>
       <c r="I5" s="72"/>
       <c r="J5" s="72"/>
@@ -9420,11 +9420,11 @@
       <c r="N5" s="71"/>
       <c r="O5" s="71"/>
     </row>
-    <row r="6" spans="1:27" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="120" t="s">
+    <row r="6" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="136" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="121"/>
+      <c r="B6" s="137"/>
       <c r="C6" s="17" t="s">
         <v>94</v>
       </c>
@@ -9436,7 +9436,7 @@
       <c r="N6" s="71"/>
       <c r="O6" s="71"/>
     </row>
-    <row r="7" spans="1:27" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>111</v>
       </c>
@@ -9453,26 +9453,26 @@
       <c r="I7" s="72"/>
       <c r="J7" s="72"/>
       <c r="K7" s="72"/>
-      <c r="L7" s="136" t="s">
+      <c r="L7" s="130" t="s">
         <v>1130</v>
       </c>
-      <c r="M7" s="137"/>
-      <c r="N7" s="137"/>
-      <c r="O7" s="138"/>
-      <c r="R7" s="136" t="s">
+      <c r="M7" s="131"/>
+      <c r="N7" s="131"/>
+      <c r="O7" s="132"/>
+      <c r="R7" s="130" t="s">
         <v>1144</v>
       </c>
-      <c r="S7" s="137"/>
-      <c r="T7" s="137"/>
-      <c r="U7" s="138"/>
-      <c r="X7" s="136" t="s">
+      <c r="S7" s="131"/>
+      <c r="T7" s="131"/>
+      <c r="U7" s="132"/>
+      <c r="X7" s="130" t="s">
         <v>1145</v>
       </c>
-      <c r="Y7" s="137"/>
-      <c r="Z7" s="137"/>
-      <c r="AA7" s="138"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="Y7" s="131"/>
+      <c r="Z7" s="131"/>
+      <c r="AA7" s="132"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>109</v>
       </c>
@@ -9485,32 +9485,32 @@
       </c>
       <c r="E8" s="87"/>
       <c r="F8" s="87"/>
-      <c r="L8" s="98" t="s">
+      <c r="L8" s="99" t="s">
         <v>1114</v>
       </c>
-      <c r="M8" s="99"/>
-      <c r="N8" s="115" t="s">
+      <c r="M8" s="100"/>
+      <c r="N8" s="128" t="s">
         <v>1117</v>
       </c>
-      <c r="O8" s="116"/>
-      <c r="R8" s="98" t="s">
+      <c r="O8" s="129"/>
+      <c r="R8" s="99" t="s">
         <v>1114</v>
       </c>
-      <c r="S8" s="99"/>
-      <c r="T8" s="115" t="s">
+      <c r="S8" s="100"/>
+      <c r="T8" s="128" t="s">
         <v>1151</v>
       </c>
-      <c r="U8" s="116"/>
-      <c r="X8" s="98" t="s">
+      <c r="U8" s="129"/>
+      <c r="X8" s="99" t="s">
         <v>1114</v>
       </c>
-      <c r="Y8" s="99"/>
-      <c r="Z8" s="115" t="s">
+      <c r="Y8" s="100"/>
+      <c r="Z8" s="128" t="s">
         <v>1156</v>
       </c>
-      <c r="AA8" s="116"/>
-    </row>
-    <row r="9" spans="1:27" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="AA8" s="129"/>
+    </row>
+    <row r="9" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>71</v>
       </c>
@@ -9523,26 +9523,26 @@
       </c>
       <c r="E9" s="87"/>
       <c r="F9" s="87"/>
-      <c r="L9" s="100"/>
-      <c r="M9" s="101"/>
-      <c r="N9" s="103">
+      <c r="L9" s="101"/>
+      <c r="M9" s="102"/>
+      <c r="N9" s="104">
         <v>0.40760000000000002</v>
       </c>
-      <c r="O9" s="101"/>
-      <c r="R9" s="100"/>
-      <c r="S9" s="101"/>
-      <c r="T9" s="103">
+      <c r="O9" s="102"/>
+      <c r="R9" s="101"/>
+      <c r="S9" s="102"/>
+      <c r="T9" s="104">
         <v>0.4047</v>
       </c>
-      <c r="U9" s="101"/>
-      <c r="X9" s="100"/>
-      <c r="Y9" s="101"/>
-      <c r="Z9" s="103" t="s">
+      <c r="U9" s="102"/>
+      <c r="X9" s="101"/>
+      <c r="Y9" s="102"/>
+      <c r="Z9" s="104" t="s">
         <v>1157</v>
       </c>
-      <c r="AA9" s="101"/>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AA9" s="102"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>68</v>
       </c>
@@ -9563,7 +9563,7 @@
       <c r="N10" s="71"/>
       <c r="O10" s="71"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>106</v>
       </c>
@@ -9585,7 +9585,7 @@
       <c r="N11" s="71"/>
       <c r="O11" s="71"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>105</v>
       </c>
@@ -9607,7 +9607,7 @@
       <c r="N12" s="71"/>
       <c r="O12" s="71"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>2</v>
       </c>
@@ -9629,7 +9629,7 @@
       <c r="N13" s="71"/>
       <c r="O13" s="71"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>103</v>
       </c>
@@ -9651,7 +9651,7 @@
       <c r="N14" s="71"/>
       <c r="O14" s="71"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>48</v>
       </c>
@@ -9665,7 +9665,7 @@
       <c r="E15" s="87"/>
       <c r="F15" s="87"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>45</v>
       </c>
@@ -9679,7 +9679,7 @@
       <c r="E16" s="87"/>
       <c r="F16" s="87"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>42</v>
       </c>
@@ -9693,7 +9693,7 @@
       <c r="E17" s="87"/>
       <c r="F17" s="87"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>39</v>
       </c>
@@ -9707,7 +9707,7 @@
       <c r="E18" s="87"/>
       <c r="F18" s="87"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>101</v>
       </c>
@@ -9721,7 +9721,7 @@
       <c r="E19" s="87"/>
       <c r="F19" s="87"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>18</v>
       </c>
@@ -9735,7 +9735,7 @@
       <c r="E20" s="87"/>
       <c r="F20" s="87"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>7</v>
       </c>
@@ -9749,7 +9749,7 @@
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>22</v>
       </c>
@@ -9763,7 +9763,7 @@
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>10</v>
       </c>
@@ -9777,7 +9777,7 @@
       <c r="E23" s="87"/>
       <c r="F23" s="87"/>
     </row>
-    <row r="24" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>13</v>
       </c>
@@ -9791,14 +9791,14 @@
       <c r="E24" s="87"/>
       <c r="F24" s="87"/>
     </row>
-    <row r="25" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="107" t="s">
+    <row r="25" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="116" t="s">
         <v>1108</v>
       </c>
-      <c r="B25" s="108"/>
-      <c r="C25" s="109"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B25" s="117"/>
+      <c r="C25" s="118"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>96</v>
       </c>
@@ -9809,7 +9809,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>93</v>
       </c>
@@ -9825,7 +9825,7 @@
       <c r="E27" s="87"/>
       <c r="F27" s="87"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>91</v>
       </c>
@@ -9841,7 +9841,7 @@
       <c r="E28" s="87"/>
       <c r="F28" s="87"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>89</v>
       </c>
@@ -9857,7 +9857,7 @@
       <c r="E29" s="87"/>
       <c r="F29" s="87"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>87</v>
       </c>
@@ -9873,7 +9873,7 @@
       <c r="E30" s="87"/>
       <c r="F30" s="87"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>85</v>
       </c>
@@ -9889,7 +9889,7 @@
       <c r="E31" s="87"/>
       <c r="F31" s="87"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>83</v>
       </c>
@@ -9905,7 +9905,7 @@
       <c r="E32" s="87"/>
       <c r="F32" s="87"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>81</v>
       </c>
@@ -9921,7 +9921,7 @@
       <c r="E33" s="87"/>
       <c r="F33" s="87"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>79</v>
       </c>
@@ -9937,7 +9937,7 @@
       <c r="E34" s="87"/>
       <c r="F34" s="87"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>77</v>
       </c>
@@ -9953,7 +9953,7 @@
       <c r="E35" s="87"/>
       <c r="F35" s="87"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>75</v>
       </c>
@@ -9969,7 +9969,7 @@
       <c r="E36" s="87"/>
       <c r="F36" s="87"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>74</v>
       </c>
@@ -9985,7 +9985,7 @@
       <c r="E37" s="87"/>
       <c r="F37" s="87"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>72</v>
       </c>
@@ -10001,7 +10001,7 @@
       <c r="E38" s="87"/>
       <c r="F38" s="87"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>69</v>
       </c>
@@ -10017,7 +10017,7 @@
       <c r="E39" s="87"/>
       <c r="F39" s="87"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>66</v>
       </c>
@@ -10033,7 +10033,7 @@
       <c r="E40" s="87"/>
       <c r="F40" s="87"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>64</v>
       </c>
@@ -10049,7 +10049,7 @@
       <c r="E41" s="87"/>
       <c r="F41" s="87"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>62</v>
       </c>
@@ -10065,7 +10065,7 @@
       <c r="E42" s="87"/>
       <c r="F42" s="87"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>60</v>
       </c>
@@ -10081,7 +10081,7 @@
       <c r="E43" s="87"/>
       <c r="F43" s="87"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>57</v>
       </c>
@@ -10097,7 +10097,7 @@
       <c r="E44" s="87"/>
       <c r="F44" s="87"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>55</v>
       </c>
@@ -10113,7 +10113,7 @@
       <c r="E45" s="87"/>
       <c r="F45" s="87"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>53</v>
       </c>
@@ -10129,7 +10129,7 @@
       <c r="E46" s="87"/>
       <c r="F46" s="87"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>51</v>
       </c>
@@ -10145,7 +10145,7 @@
       <c r="E47" s="87"/>
       <c r="F47" s="87"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>49</v>
       </c>
@@ -10161,7 +10161,7 @@
       <c r="E48" s="87"/>
       <c r="F48" s="87"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>46</v>
       </c>
@@ -10177,7 +10177,7 @@
       <c r="E49" s="87"/>
       <c r="F49" s="87"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>43</v>
       </c>
@@ -10193,7 +10193,7 @@
       <c r="E50" s="87"/>
       <c r="F50" s="87"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>40</v>
       </c>
@@ -10209,7 +10209,7 @@
       <c r="E51" s="87"/>
       <c r="F51" s="87"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>37</v>
       </c>
@@ -10225,7 +10225,7 @@
       <c r="E52" s="87"/>
       <c r="F52" s="87"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>35</v>
       </c>
@@ -10241,7 +10241,7 @@
       <c r="E53" s="87"/>
       <c r="F53" s="87"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>33</v>
       </c>
@@ -10257,7 +10257,7 @@
       <c r="E54" s="87"/>
       <c r="F54" s="87"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>31</v>
       </c>
@@ -10273,7 +10273,7 @@
       <c r="E55" s="87"/>
       <c r="F55" s="87"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>29</v>
       </c>
@@ -10289,7 +10289,7 @@
       <c r="E56" s="87"/>
       <c r="F56" s="87"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>27</v>
       </c>
@@ -10305,7 +10305,7 @@
       <c r="E57" s="87"/>
       <c r="F57" s="87"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>25</v>
       </c>
@@ -10321,7 +10321,7 @@
       <c r="E58" s="87"/>
       <c r="F58" s="87"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>23</v>
       </c>
@@ -10337,7 +10337,7 @@
       <c r="E59" s="87"/>
       <c r="F59" s="87"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>20</v>
       </c>
@@ -10353,7 +10353,7 @@
       <c r="E60" s="87"/>
       <c r="F60" s="87"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>19</v>
       </c>
@@ -10369,7 +10369,7 @@
       <c r="E61" s="87"/>
       <c r="F61" s="87"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>16</v>
       </c>
@@ -10385,7 +10385,7 @@
       <c r="E62" s="87"/>
       <c r="F62" s="87"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>14</v>
       </c>
@@ -10401,7 +10401,7 @@
       <c r="E63" s="87"/>
       <c r="F63" s="87"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>11</v>
       </c>
@@ -10417,7 +10417,7 @@
       <c r="E64" s="87"/>
       <c r="F64" s="87"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>8</v>
       </c>
@@ -10433,7 +10433,7 @@
       <c r="E65" s="87"/>
       <c r="F65" s="87"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>5</v>
       </c>
@@ -10449,7 +10449,7 @@
       <c r="E66" s="87"/>
       <c r="F66" s="87"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>5</v>
       </c>
@@ -10465,7 +10465,7 @@
       <c r="E67" s="87"/>
       <c r="F67" s="87"/>
     </row>
-    <row r="68" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="11" t="s">
         <v>3</v>
       </c>
@@ -10483,6 +10483,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="L8:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="R7:U7"/>
     <mergeCell ref="R8:S9"/>
     <mergeCell ref="T8:U8"/>
     <mergeCell ref="T9:U9"/>
@@ -10490,16 +10500,6 @@
     <mergeCell ref="X8:Y9"/>
     <mergeCell ref="Z8:AA8"/>
     <mergeCell ref="Z9:AA9"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="R7:U7"/>
-    <mergeCell ref="L8:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10510,17 +10510,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{188EC796-F922-4664-8A65-E4BA79E26EBA}">
   <dimension ref="A1:AC33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="79.3984375" customWidth="1"/>
+    <col min="3" max="3" width="79.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="122" t="s">
+    <row r="1" spans="1:29" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="138" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="124"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="140"/>
       <c r="D1" s="86" t="s">
         <v>1130</v>
       </c>
@@ -10536,19 +10536,19 @@
       <c r="L1" s="74"/>
       <c r="M1" s="74"/>
     </row>
-    <row r="2" spans="1:29" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="125" t="s">
+    <row r="2" spans="1:29" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="141" t="s">
         <v>1115</v>
       </c>
-      <c r="B2" s="126"/>
-      <c r="C2" s="127"/>
+      <c r="B2" s="142"/>
+      <c r="C2" s="143"/>
       <c r="I2" s="72"/>
       <c r="J2" s="72"/>
       <c r="K2" s="73"/>
       <c r="L2" s="73"/>
       <c r="M2" s="73"/>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>113</v>
       </c>
@@ -10564,7 +10564,7 @@
       <c r="L3" s="73"/>
       <c r="M3" s="73"/>
     </row>
-    <row r="4" spans="1:29" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>20002</v>
       </c>
@@ -10589,19 +10589,19 @@
       <c r="L4" s="72"/>
       <c r="M4" s="72"/>
     </row>
-    <row r="5" spans="1:29" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A5" s="95" t="s">
+    <row r="5" spans="1:29" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="106" t="s">
         <v>1107</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="97"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="108"/>
       <c r="I5" s="73"/>
       <c r="J5" s="73"/>
       <c r="K5" s="72"/>
       <c r="L5" s="72"/>
       <c r="M5" s="72"/>
     </row>
-    <row r="6" spans="1:29" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="30" t="s">
         <v>95</v>
       </c>
@@ -10614,26 +10614,26 @@
       <c r="K6" s="72"/>
       <c r="L6" s="72"/>
       <c r="M6" s="72"/>
-      <c r="N6" s="142" t="s">
+      <c r="N6" s="109" t="s">
         <v>1130</v>
       </c>
-      <c r="O6" s="143"/>
-      <c r="P6" s="143"/>
-      <c r="Q6" s="144"/>
-      <c r="T6" s="142" t="s">
+      <c r="O6" s="110"/>
+      <c r="P6" s="110"/>
+      <c r="Q6" s="111"/>
+      <c r="T6" s="109" t="s">
         <v>1144</v>
       </c>
-      <c r="U6" s="143"/>
-      <c r="V6" s="143"/>
-      <c r="W6" s="144"/>
-      <c r="Z6" s="142" t="s">
+      <c r="U6" s="110"/>
+      <c r="V6" s="110"/>
+      <c r="W6" s="111"/>
+      <c r="Z6" s="109" t="s">
         <v>1150</v>
       </c>
-      <c r="AA6" s="143"/>
-      <c r="AB6" s="143"/>
-      <c r="AC6" s="144"/>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AA6" s="110"/>
+      <c r="AB6" s="110"/>
+      <c r="AC6" s="111"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>246</v>
       </c>
@@ -10648,32 +10648,32 @@
       <c r="F7" s="87"/>
       <c r="L7" s="73"/>
       <c r="M7" s="75"/>
-      <c r="N7" s="98" t="s">
+      <c r="N7" s="99" t="s">
         <v>245</v>
       </c>
-      <c r="O7" s="99"/>
-      <c r="P7" s="115" t="s">
+      <c r="O7" s="100"/>
+      <c r="P7" s="128" t="s">
         <v>1118</v>
       </c>
-      <c r="Q7" s="116"/>
-      <c r="T7" s="98" t="s">
+      <c r="Q7" s="129"/>
+      <c r="T7" s="99" t="s">
         <v>245</v>
       </c>
-      <c r="U7" s="99"/>
-      <c r="V7" s="115" t="s">
+      <c r="U7" s="100"/>
+      <c r="V7" s="128" t="s">
         <v>1118</v>
       </c>
-      <c r="W7" s="116"/>
-      <c r="Z7" s="98" t="s">
+      <c r="W7" s="129"/>
+      <c r="Z7" s="99" t="s">
         <v>245</v>
       </c>
-      <c r="AA7" s="99"/>
-      <c r="AB7" s="115" t="s">
+      <c r="AA7" s="100"/>
+      <c r="AB7" s="128" t="s">
         <v>1158</v>
       </c>
-      <c r="AC7" s="116"/>
-    </row>
-    <row r="8" spans="1:29" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="AC7" s="129"/>
+    </row>
+    <row r="8" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="s">
         <v>248</v>
       </c>
@@ -10686,26 +10686,26 @@
       </c>
       <c r="E8" s="87"/>
       <c r="F8" s="87"/>
-      <c r="N8" s="100"/>
-      <c r="O8" s="101"/>
-      <c r="P8" s="103">
+      <c r="N8" s="101"/>
+      <c r="O8" s="102"/>
+      <c r="P8" s="104">
         <v>2.06E-2</v>
       </c>
-      <c r="Q8" s="101"/>
-      <c r="T8" s="100"/>
-      <c r="U8" s="101"/>
-      <c r="V8" s="103">
+      <c r="Q8" s="102"/>
+      <c r="T8" s="101"/>
+      <c r="U8" s="102"/>
+      <c r="V8" s="104">
         <v>2.06E-2</v>
       </c>
-      <c r="W8" s="101"/>
-      <c r="Z8" s="100"/>
-      <c r="AA8" s="101"/>
-      <c r="AB8" s="103">
+      <c r="W8" s="102"/>
+      <c r="Z8" s="101"/>
+      <c r="AA8" s="102"/>
+      <c r="AB8" s="104">
         <v>1.78E-2</v>
       </c>
-      <c r="AC8" s="101"/>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC8" s="102"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>250</v>
       </c>
@@ -10719,7 +10719,7 @@
       <c r="E9" s="87"/>
       <c r="F9" s="87"/>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>252</v>
       </c>
@@ -10733,7 +10733,7 @@
       <c r="E10" s="87"/>
       <c r="F10" s="87"/>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
         <v>254</v>
       </c>
@@ -10747,7 +10747,7 @@
       <c r="E11" s="87"/>
       <c r="F11" s="87"/>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
         <v>256</v>
       </c>
@@ -10761,7 +10761,7 @@
       <c r="E12" s="87"/>
       <c r="F12" s="87"/>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
         <v>258</v>
       </c>
@@ -10775,7 +10775,7 @@
       <c r="E13" s="87"/>
       <c r="F13" s="87"/>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
         <v>260</v>
       </c>
@@ -10789,7 +10789,7 @@
       <c r="E14" s="87"/>
       <c r="F14" s="87"/>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
         <v>262</v>
       </c>
@@ -10803,7 +10803,7 @@
       <c r="E15" s="87"/>
       <c r="F15" s="87"/>
     </row>
-    <row r="16" spans="1:29" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="29" t="s">
         <v>264</v>
       </c>
@@ -10817,14 +10817,14 @@
       <c r="E16" s="87"/>
       <c r="F16" s="87"/>
     </row>
-    <row r="17" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="95" t="s">
+    <row r="17" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="106" t="s">
         <v>1108</v>
       </c>
-      <c r="B17" s="96"/>
-      <c r="C17" s="97"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B17" s="107"/>
+      <c r="C17" s="108"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>96</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>266</v>
       </c>
@@ -10851,7 +10851,7 @@
       <c r="E19" s="87"/>
       <c r="F19" s="87"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>268</v>
       </c>
@@ -10867,7 +10867,7 @@
       <c r="E20" s="87"/>
       <c r="F20" s="87"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>270</v>
       </c>
@@ -10883,7 +10883,7 @@
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>272</v>
       </c>
@@ -10899,7 +10899,7 @@
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>274</v>
       </c>
@@ -10915,7 +10915,7 @@
       <c r="E23" s="87"/>
       <c r="F23" s="87"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>276</v>
       </c>
@@ -10931,7 +10931,7 @@
       <c r="E24" s="87"/>
       <c r="F24" s="87"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>278</v>
       </c>
@@ -10947,7 +10947,7 @@
       <c r="E25" s="87"/>
       <c r="F25" s="87"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>280</v>
       </c>
@@ -10963,7 +10963,7 @@
       <c r="E26" s="87"/>
       <c r="F26" s="87"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>282</v>
       </c>
@@ -10979,7 +10979,7 @@
       <c r="E27" s="87"/>
       <c r="F27" s="87"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>284</v>
       </c>
@@ -10995,7 +10995,7 @@
       <c r="E28" s="87"/>
       <c r="F28" s="87"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>286</v>
       </c>
@@ -11011,7 +11011,7 @@
       <c r="E29" s="87"/>
       <c r="F29" s="87"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>288</v>
       </c>
@@ -11027,7 +11027,7 @@
       <c r="E30" s="87"/>
       <c r="F30" s="87"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>290</v>
       </c>
@@ -11043,7 +11043,7 @@
       <c r="E31" s="87"/>
       <c r="F31" s="87"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>292</v>
       </c>
@@ -11059,7 +11059,7 @@
       <c r="E32" s="87"/>
       <c r="F32" s="87"/>
     </row>
-    <row r="33" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>294</v>
       </c>
@@ -11077,6 +11077,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="N7:O8"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="N6:Q6"/>
     <mergeCell ref="T6:W6"/>
     <mergeCell ref="T7:U8"/>
     <mergeCell ref="V7:W7"/>
@@ -11085,14 +11093,6 @@
     <mergeCell ref="Z7:AA8"/>
     <mergeCell ref="AB7:AC7"/>
     <mergeCell ref="AB8:AC8"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="N7:O8"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="N6:Q6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11102,19 +11102,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E4FB2F6-565F-45BC-9085-547A1F6D04C4}">
   <dimension ref="A1:AA82"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="108.3984375" customWidth="1"/>
+    <col min="3" max="3" width="108.42578125" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="8" max="8" width="12.265625" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:27" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="122" t="s">
         <v>1116</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="106"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="124"/>
       <c r="D1" s="86" t="s">
         <v>1130</v>
       </c>
@@ -11132,12 +11132,12 @@
       <c r="L1" s="65"/>
       <c r="M1" s="65"/>
     </row>
-    <row r="2" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="95" t="s">
+    <row r="2" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="106" t="s">
         <v>1111</v>
       </c>
-      <c r="B2" s="96"/>
-      <c r="C2" s="97"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="108"/>
       <c r="F2" s="65"/>
       <c r="G2" s="72"/>
       <c r="H2" s="72"/>
@@ -11147,7 +11147,7 @@
       <c r="L2" s="82"/>
       <c r="M2" s="82"/>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>113</v>
       </c>
@@ -11160,13 +11160,13 @@
       <c r="F3" s="65"/>
       <c r="G3" s="72"/>
       <c r="H3" s="72"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="K3" s="128"/>
+      <c r="I3" s="152"/>
+      <c r="J3" s="152"/>
+      <c r="K3" s="152"/>
       <c r="L3" s="72"/>
       <c r="M3" s="72"/>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>3894</v>
       </c>
@@ -11189,12 +11189,12 @@
       <c r="L4" s="72"/>
       <c r="M4" s="72"/>
     </row>
-    <row r="5" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="129" t="s">
+    <row r="5" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="147" t="s">
         <v>1112</v>
       </c>
-      <c r="B5" s="130"/>
-      <c r="C5" s="131"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="149"/>
       <c r="F5" s="65"/>
       <c r="G5" s="77"/>
       <c r="H5" s="72"/>
@@ -11204,7 +11204,7 @@
       <c r="L5" s="73"/>
       <c r="M5" s="73"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
         <v>113</v>
       </c>
@@ -11223,7 +11223,7 @@
       <c r="L6" s="73"/>
       <c r="M6" s="73"/>
     </row>
-    <row r="7" spans="1:27" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>20002</v>
       </c>
@@ -11250,12 +11250,12 @@
       <c r="L7" s="65"/>
       <c r="M7" s="79"/>
     </row>
-    <row r="8" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="107" t="s">
+    <row r="8" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="116" t="s">
         <v>1107</v>
       </c>
-      <c r="B8" s="108"/>
-      <c r="C8" s="109"/>
+      <c r="B8" s="117"/>
+      <c r="C8" s="118"/>
       <c r="F8" s="65"/>
       <c r="G8" s="72"/>
       <c r="H8" s="72"/>
@@ -11265,11 +11265,11 @@
       <c r="L8" s="78"/>
       <c r="M8" s="73"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.45">
-      <c r="A9" s="132" t="s">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="150" t="s">
         <v>95</v>
       </c>
-      <c r="B9" s="133"/>
+      <c r="B9" s="151"/>
       <c r="C9" s="27" t="s">
         <v>94</v>
       </c>
@@ -11282,7 +11282,7 @@
       <c r="L9" s="73"/>
       <c r="M9" s="73"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>116</v>
       </c>
@@ -11303,7 +11303,7 @@
       <c r="L10" s="78"/>
       <c r="M10" s="81"/>
     </row>
-    <row r="11" spans="1:27" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>118</v>
       </c>
@@ -11324,7 +11324,7 @@
       <c r="L11" s="65"/>
       <c r="M11" s="65"/>
     </row>
-    <row r="12" spans="1:27" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>120</v>
       </c>
@@ -11342,26 +11342,26 @@
       <c r="I12" s="65"/>
       <c r="J12" s="65"/>
       <c r="K12" s="65"/>
-      <c r="L12" s="145" t="s">
+      <c r="L12" s="144" t="s">
         <v>1130</v>
       </c>
-      <c r="M12" s="146"/>
-      <c r="N12" s="146"/>
-      <c r="O12" s="147"/>
-      <c r="R12" s="145" t="s">
+      <c r="M12" s="145"/>
+      <c r="N12" s="145"/>
+      <c r="O12" s="146"/>
+      <c r="R12" s="144" t="s">
         <v>1144</v>
       </c>
-      <c r="S12" s="146"/>
-      <c r="T12" s="146"/>
-      <c r="U12" s="147"/>
-      <c r="X12" s="145" t="s">
+      <c r="S12" s="145"/>
+      <c r="T12" s="145"/>
+      <c r="U12" s="146"/>
+      <c r="X12" s="144" t="s">
         <v>1145</v>
       </c>
-      <c r="Y12" s="146"/>
-      <c r="Z12" s="146"/>
-      <c r="AA12" s="147"/>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="Y12" s="145"/>
+      <c r="Z12" s="145"/>
+      <c r="AA12" s="146"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>122</v>
       </c>
@@ -11374,32 +11374,32 @@
       </c>
       <c r="E13" s="87"/>
       <c r="F13" s="87"/>
-      <c r="L13" s="98" t="s">
+      <c r="L13" s="99" t="s">
         <v>1116</v>
       </c>
-      <c r="M13" s="99"/>
-      <c r="N13" s="115" t="s">
+      <c r="M13" s="100"/>
+      <c r="N13" s="128" t="s">
         <v>1119</v>
       </c>
-      <c r="O13" s="116"/>
-      <c r="R13" s="98" t="s">
+      <c r="O13" s="129"/>
+      <c r="R13" s="99" t="s">
         <v>1116</v>
       </c>
-      <c r="S13" s="99"/>
-      <c r="T13" s="115" t="s">
+      <c r="S13" s="100"/>
+      <c r="T13" s="128" t="s">
         <v>1148</v>
       </c>
-      <c r="U13" s="116"/>
-      <c r="X13" s="98" t="s">
+      <c r="U13" s="129"/>
+      <c r="X13" s="99" t="s">
         <v>1116</v>
       </c>
-      <c r="Y13" s="99"/>
-      <c r="Z13" s="115" t="s">
+      <c r="Y13" s="100"/>
+      <c r="Z13" s="128" t="s">
         <v>1159</v>
       </c>
-      <c r="AA13" s="116"/>
-    </row>
-    <row r="14" spans="1:27" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="AA13" s="129"/>
+    </row>
+    <row r="14" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>124</v>
       </c>
@@ -11412,26 +11412,26 @@
       </c>
       <c r="E14" s="87"/>
       <c r="F14" s="87"/>
-      <c r="L14" s="100"/>
-      <c r="M14" s="101"/>
-      <c r="N14" s="103" t="s">
+      <c r="L14" s="101"/>
+      <c r="M14" s="102"/>
+      <c r="N14" s="104" t="s">
         <v>1120</v>
       </c>
-      <c r="O14" s="101"/>
-      <c r="R14" s="100"/>
-      <c r="S14" s="101"/>
-      <c r="T14" s="103" t="s">
+      <c r="O14" s="102"/>
+      <c r="R14" s="101"/>
+      <c r="S14" s="102"/>
+      <c r="T14" s="104" t="s">
         <v>1149</v>
       </c>
-      <c r="U14" s="101"/>
-      <c r="X14" s="100"/>
-      <c r="Y14" s="101"/>
-      <c r="Z14" s="103" t="s">
+      <c r="U14" s="102"/>
+      <c r="X14" s="101"/>
+      <c r="Y14" s="102"/>
+      <c r="Z14" s="104" t="s">
         <v>1160</v>
       </c>
-      <c r="AA14" s="101"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AA14" s="102"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>126</v>
       </c>
@@ -11445,7 +11445,7 @@
       <c r="E15" s="87"/>
       <c r="F15" s="87"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>128</v>
       </c>
@@ -11459,7 +11459,7 @@
       <c r="E16" s="87"/>
       <c r="F16" s="87"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>130</v>
       </c>
@@ -11473,7 +11473,7 @@
       <c r="E17" s="87"/>
       <c r="F17" s="87"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>132</v>
       </c>
@@ -11487,7 +11487,7 @@
       <c r="E18" s="87"/>
       <c r="F18" s="87"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>134</v>
       </c>
@@ -11501,7 +11501,7 @@
       <c r="E19" s="87"/>
       <c r="F19" s="87"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>136</v>
       </c>
@@ -11515,7 +11515,7 @@
       <c r="E20" s="87"/>
       <c r="F20" s="87"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>138</v>
       </c>
@@ -11529,7 +11529,7 @@
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>140</v>
       </c>
@@ -11550,7 +11550,7 @@
         <v>11590</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>142</v>
       </c>
@@ -11571,7 +11571,7 @@
         <v>16639</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>144</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>146</v>
       </c>
@@ -11606,7 +11606,7 @@
       <c r="E25" s="87"/>
       <c r="F25" s="87"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>148</v>
       </c>
@@ -11620,7 +11620,7 @@
       <c r="E26" s="87"/>
       <c r="F26" s="87"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>150</v>
       </c>
@@ -11634,7 +11634,7 @@
       <c r="E27" s="87"/>
       <c r="F27" s="87"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>152</v>
       </c>
@@ -11648,7 +11648,7 @@
       <c r="E28" s="87"/>
       <c r="F28" s="87"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>154</v>
       </c>
@@ -11662,7 +11662,7 @@
       <c r="E29" s="87"/>
       <c r="F29" s="87"/>
     </row>
-    <row r="30" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>156</v>
       </c>
@@ -11676,14 +11676,14 @@
       <c r="E30" s="87"/>
       <c r="F30" s="87"/>
     </row>
-    <row r="31" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="107" t="s">
+    <row r="31" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="116" t="s">
         <v>1108</v>
       </c>
-      <c r="B31" s="108"/>
-      <c r="C31" s="109"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B31" s="117"/>
+      <c r="C31" s="118"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="24" t="s">
         <v>96</v>
       </c>
@@ -11694,7 +11694,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>158</v>
       </c>
@@ -11710,7 +11710,7 @@
       <c r="E33" s="87"/>
       <c r="F33" s="87"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>160</v>
       </c>
@@ -11726,7 +11726,7 @@
       <c r="E34" s="87"/>
       <c r="F34" s="87"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>162</v>
       </c>
@@ -11742,7 +11742,7 @@
       <c r="E35" s="87"/>
       <c r="F35" s="87"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>164</v>
       </c>
@@ -11758,7 +11758,7 @@
       <c r="E36" s="87"/>
       <c r="F36" s="87"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>166</v>
       </c>
@@ -11774,7 +11774,7 @@
       <c r="E37" s="87"/>
       <c r="F37" s="87"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>168</v>
       </c>
@@ -11790,7 +11790,7 @@
       <c r="E38" s="87"/>
       <c r="F38" s="87"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>170</v>
       </c>
@@ -11806,7 +11806,7 @@
       <c r="E39" s="87"/>
       <c r="F39" s="87"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>172</v>
       </c>
@@ -11822,7 +11822,7 @@
       <c r="E40" s="87"/>
       <c r="F40" s="87"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>174</v>
       </c>
@@ -11838,7 +11838,7 @@
       <c r="E41" s="87"/>
       <c r="F41" s="87"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>176</v>
       </c>
@@ -11854,7 +11854,7 @@
       <c r="E42" s="87"/>
       <c r="F42" s="87"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>178</v>
       </c>
@@ -11870,7 +11870,7 @@
       <c r="E43" s="87"/>
       <c r="F43" s="87"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>180</v>
       </c>
@@ -11886,7 +11886,7 @@
       <c r="E44" s="87"/>
       <c r="F44" s="87"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>182</v>
       </c>
@@ -11902,7 +11902,7 @@
       <c r="E45" s="87"/>
       <c r="F45" s="87"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>184</v>
       </c>
@@ -11918,7 +11918,7 @@
       <c r="E46" s="87"/>
       <c r="F46" s="87"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>186</v>
       </c>
@@ -11934,7 +11934,7 @@
       <c r="E47" s="87"/>
       <c r="F47" s="87"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>188</v>
       </c>
@@ -11950,7 +11950,7 @@
       <c r="E48" s="87"/>
       <c r="F48" s="87"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>190</v>
       </c>
@@ -11966,7 +11966,7 @@
       <c r="E49" s="87"/>
       <c r="F49" s="87"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>192</v>
       </c>
@@ -11982,7 +11982,7 @@
       <c r="E50" s="87"/>
       <c r="F50" s="87"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>193</v>
       </c>
@@ -11998,7 +11998,7 @@
       <c r="E51" s="87"/>
       <c r="F51" s="87"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>195</v>
       </c>
@@ -12014,7 +12014,7 @@
       <c r="E52" s="87"/>
       <c r="F52" s="87"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>197</v>
       </c>
@@ -12030,7 +12030,7 @@
       <c r="E53" s="87"/>
       <c r="F53" s="87"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>199</v>
       </c>
@@ -12046,7 +12046,7 @@
       <c r="E54" s="87"/>
       <c r="F54" s="87"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>201</v>
       </c>
@@ -12062,7 +12062,7 @@
       <c r="E55" s="87"/>
       <c r="F55" s="87"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>203</v>
       </c>
@@ -12078,7 +12078,7 @@
       <c r="E56" s="87"/>
       <c r="F56" s="87"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>205</v>
       </c>
@@ -12094,7 +12094,7 @@
       <c r="E57" s="87"/>
       <c r="F57" s="87"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
         <v>207</v>
       </c>
@@ -12110,7 +12110,7 @@
       <c r="E58" s="87"/>
       <c r="F58" s="87"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
         <v>208</v>
       </c>
@@ -12126,7 +12126,7 @@
       <c r="E59" s="87"/>
       <c r="F59" s="87"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
         <v>209</v>
       </c>
@@ -12142,7 +12142,7 @@
       <c r="E60" s="87"/>
       <c r="F60" s="87"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
         <v>210</v>
       </c>
@@ -12158,7 +12158,7 @@
       <c r="E61" s="87"/>
       <c r="F61" s="87"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>211</v>
       </c>
@@ -12174,7 +12174,7 @@
       <c r="E62" s="87"/>
       <c r="F62" s="87"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>212</v>
       </c>
@@ -12190,7 +12190,7 @@
       <c r="E63" s="87"/>
       <c r="F63" s="87"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>213</v>
       </c>
@@ -12206,7 +12206,7 @@
       <c r="E64" s="87"/>
       <c r="F64" s="87"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>214</v>
       </c>
@@ -12222,7 +12222,7 @@
       <c r="E65" s="87"/>
       <c r="F65" s="87"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>215</v>
       </c>
@@ -12238,7 +12238,7 @@
       <c r="E66" s="87"/>
       <c r="F66" s="87"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>216</v>
       </c>
@@ -12254,7 +12254,7 @@
       <c r="E67" s="87"/>
       <c r="F67" s="87"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>217</v>
       </c>
@@ -12270,7 +12270,7 @@
       <c r="E68" s="87"/>
       <c r="F68" s="87"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
         <v>219</v>
       </c>
@@ -12286,7 +12286,7 @@
       <c r="E69" s="87"/>
       <c r="F69" s="87"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
         <v>220</v>
       </c>
@@ -12302,7 +12302,7 @@
       <c r="E70" s="87"/>
       <c r="F70" s="87"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
         <v>221</v>
       </c>
@@ -12318,7 +12318,7 @@
       <c r="E71" s="87"/>
       <c r="F71" s="87"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
         <v>223</v>
       </c>
@@ -12334,7 +12334,7 @@
       <c r="E72" s="87"/>
       <c r="F72" s="87"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>225</v>
       </c>
@@ -12350,7 +12350,7 @@
       <c r="E73" s="87"/>
       <c r="F73" s="87"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>227</v>
       </c>
@@ -12366,7 +12366,7 @@
       <c r="E74" s="87"/>
       <c r="F74" s="87"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
         <v>229</v>
       </c>
@@ -12382,7 +12382,7 @@
       <c r="E75" s="87"/>
       <c r="F75" s="87"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
         <v>231</v>
       </c>
@@ -12398,7 +12398,7 @@
       <c r="E76" s="87"/>
       <c r="F76" s="87"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>233</v>
       </c>
@@ -12414,7 +12414,7 @@
       <c r="E77" s="87"/>
       <c r="F77" s="87"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>235</v>
       </c>
@@ -12430,7 +12430,7 @@
       <c r="E78" s="87"/>
       <c r="F78" s="87"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>237</v>
       </c>
@@ -12446,7 +12446,7 @@
       <c r="E79" s="87"/>
       <c r="F79" s="87"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
         <v>239</v>
       </c>
@@ -12462,7 +12462,7 @@
       <c r="E80" s="87"/>
       <c r="F80" s="87"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
         <v>241</v>
       </c>
@@ -12478,7 +12478,7 @@
       <c r="E81" s="87"/>
       <c r="F81" s="87"/>
     </row>
-    <row r="82" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
         <v>243</v>
       </c>
@@ -12496,6 +12496,17 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="L13:M14"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="L12:O12"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="R12:U12"/>
     <mergeCell ref="R13:S14"/>
     <mergeCell ref="T13:U13"/>
@@ -12504,17 +12515,6 @@
     <mergeCell ref="X13:Y14"/>
     <mergeCell ref="Z13:AA13"/>
     <mergeCell ref="Z14:AA14"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="L13:M14"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="L12:O12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12524,18 +12524,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67EC9F79-357D-46C4-ADF8-63FAF8E66FAE}">
   <dimension ref="A1:AB194"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="55.1328125" customWidth="1"/>
-    <col min="4" max="4" width="56.59765625" customWidth="1"/>
+    <col min="3" max="3" width="55.140625" customWidth="1"/>
+    <col min="4" max="4" width="56.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:28" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="122" t="s">
         <v>1121</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="106"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="124"/>
       <c r="D1" s="8"/>
       <c r="E1" s="86" t="s">
         <v>1130</v>
@@ -12547,15 +12547,15 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="110" t="s">
+    <row r="2" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="125" t="s">
         <v>1111</v>
       </c>
-      <c r="B2" s="111"/>
-      <c r="C2" s="112"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="127"/>
       <c r="D2" s="8"/>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>113</v>
       </c>
@@ -12566,11 +12566,11 @@
         <v>94</v>
       </c>
       <c r="D3" s="8"/>
-      <c r="F3" s="141" t="s">
+      <c r="F3" s="95" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2443</v>
       </c>
@@ -12586,18 +12586,18 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="26.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="110" t="s">
+    <row r="5" spans="1:28" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="125" t="s">
         <v>1122</v>
       </c>
-      <c r="B5" s="111"/>
-      <c r="C5" s="112"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="127"/>
       <c r="D5" s="8"/>
       <c r="F5" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
         <v>113</v>
       </c>
@@ -12616,7 +12616,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>20002</v>
       </c>
@@ -12626,58 +12626,58 @@
       <c r="C7" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="M7" s="142" t="s">
+      <c r="M7" s="109" t="s">
         <v>1130</v>
       </c>
-      <c r="N7" s="143"/>
-      <c r="O7" s="143"/>
-      <c r="P7" s="144"/>
-      <c r="S7" s="142" t="s">
+      <c r="N7" s="110"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="111"/>
+      <c r="S7" s="109" t="s">
         <v>1144</v>
       </c>
-      <c r="T7" s="143"/>
-      <c r="U7" s="143"/>
-      <c r="V7" s="144"/>
-      <c r="Y7" s="142" t="s">
+      <c r="T7" s="110"/>
+      <c r="U7" s="110"/>
+      <c r="V7" s="111"/>
+      <c r="Y7" s="109" t="s">
         <v>1145</v>
       </c>
-      <c r="Z7" s="143"/>
-      <c r="AA7" s="143"/>
-      <c r="AB7" s="144"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A8" s="110" t="s">
+      <c r="Z7" s="110"/>
+      <c r="AA7" s="110"/>
+      <c r="AB7" s="111"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="125" t="s">
         <v>1123</v>
       </c>
-      <c r="B8" s="111"/>
-      <c r="C8" s="112"/>
+      <c r="B8" s="126"/>
+      <c r="C8" s="127"/>
       <c r="D8" s="8"/>
-      <c r="M8" s="98" t="s">
+      <c r="M8" s="99" t="s">
         <v>1133</v>
       </c>
-      <c r="N8" s="99"/>
-      <c r="O8" s="115" t="s">
+      <c r="N8" s="100"/>
+      <c r="O8" s="128" t="s">
         <v>1142</v>
       </c>
-      <c r="P8" s="116"/>
-      <c r="S8" s="98" t="s">
+      <c r="P8" s="129"/>
+      <c r="S8" s="99" t="s">
         <v>1133</v>
       </c>
-      <c r="T8" s="99"/>
-      <c r="U8" s="115" t="s">
+      <c r="T8" s="100"/>
+      <c r="U8" s="128" t="s">
         <v>1146</v>
       </c>
-      <c r="V8" s="116"/>
-      <c r="Y8" s="98" t="s">
+      <c r="V8" s="129"/>
+      <c r="Y8" s="99" t="s">
         <v>1133</v>
       </c>
-      <c r="Z8" s="99"/>
-      <c r="AA8" s="115" t="s">
+      <c r="Z8" s="100"/>
+      <c r="AA8" s="128" t="s">
         <v>1161</v>
       </c>
-      <c r="AB8" s="116"/>
-    </row>
-    <row r="9" spans="1:28" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="AB8" s="129"/>
+    </row>
+    <row r="9" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
         <v>113</v>
       </c>
@@ -12688,33 +12688,33 @@
         <v>94</v>
       </c>
       <c r="D9" s="8"/>
-      <c r="E9" s="140">
+      <c r="E9" s="154">
         <v>6443</v>
       </c>
-      <c r="F9" s="113" t="s">
+      <c r="F9" s="119" t="s">
         <v>1141</v>
       </c>
-      <c r="G9" s="113"/>
-      <c r="M9" s="100"/>
-      <c r="N9" s="101"/>
-      <c r="O9" s="103" t="s">
+      <c r="G9" s="119"/>
+      <c r="M9" s="101"/>
+      <c r="N9" s="102"/>
+      <c r="O9" s="104" t="s">
         <v>1143</v>
       </c>
-      <c r="P9" s="101"/>
-      <c r="S9" s="100"/>
-      <c r="T9" s="101"/>
-      <c r="U9" s="103" t="s">
+      <c r="P9" s="102"/>
+      <c r="S9" s="101"/>
+      <c r="T9" s="102"/>
+      <c r="U9" s="104" t="s">
         <v>1147</v>
       </c>
-      <c r="V9" s="101"/>
-      <c r="Y9" s="100"/>
-      <c r="Z9" s="101"/>
-      <c r="AA9" s="103" t="s">
+      <c r="V9" s="102"/>
+      <c r="Y9" s="101"/>
+      <c r="Z9" s="102"/>
+      <c r="AA9" s="104" t="s">
         <v>1162</v>
       </c>
-      <c r="AB9" s="101"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AB9" s="102"/>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>20003</v>
       </c>
@@ -12724,11 +12724,11 @@
       <c r="C10" s="34" t="s">
         <v>298</v>
       </c>
-      <c r="E10" s="140"/>
-      <c r="F10" s="113"/>
-      <c r="G10" s="113"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="E10" s="154"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="119"/>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>20003</v>
       </c>
@@ -12738,11 +12738,11 @@
       <c r="C11" s="34" t="s">
         <v>299</v>
       </c>
-      <c r="E11" s="140"/>
-      <c r="F11" s="113"/>
-      <c r="G11" s="113"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="E11" s="154"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="119"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="33">
         <v>20003</v>
       </c>
@@ -12752,11 +12752,11 @@
       <c r="C12" s="34" t="s">
         <v>300</v>
       </c>
-      <c r="E12" s="140"/>
-      <c r="F12" s="113"/>
-      <c r="G12" s="113"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="E12" s="154"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="119"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="33">
         <v>20003</v>
       </c>
@@ -12766,11 +12766,11 @@
       <c r="C13" s="34" t="s">
         <v>301</v>
       </c>
-      <c r="E13" s="140"/>
-      <c r="F13" s="113"/>
-      <c r="G13" s="113"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="E13" s="154"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="119"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="33">
         <v>20003</v>
       </c>
@@ -12780,11 +12780,11 @@
       <c r="C14" s="34" t="s">
         <v>302</v>
       </c>
-      <c r="E14" s="140"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="113"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="E14" s="154"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="33">
         <v>20003</v>
       </c>
@@ -12794,11 +12794,11 @@
       <c r="C15" s="34" t="s">
         <v>303</v>
       </c>
-      <c r="E15" s="140"/>
-      <c r="F15" s="113"/>
-      <c r="G15" s="113"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="E15" s="154"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="33">
         <v>20003</v>
       </c>
@@ -12808,11 +12808,11 @@
       <c r="C16" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="E16" s="140"/>
-      <c r="F16" s="113"/>
-      <c r="G16" s="113"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E16" s="154"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>20003</v>
       </c>
@@ -12822,11 +12822,11 @@
       <c r="C17" s="34" t="s">
         <v>305</v>
       </c>
-      <c r="E17" s="140"/>
-      <c r="F17" s="113"/>
-      <c r="G17" s="113"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E17" s="154"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="119"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="33">
         <v>20003</v>
       </c>
@@ -12836,11 +12836,11 @@
       <c r="C18" s="34" t="s">
         <v>306</v>
       </c>
-      <c r="E18" s="140"/>
-      <c r="F18" s="113"/>
-      <c r="G18" s="113"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E18" s="154"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="119"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="33">
         <v>20003</v>
       </c>
@@ -12850,11 +12850,11 @@
       <c r="C19" s="34" t="s">
         <v>307</v>
       </c>
-      <c r="E19" s="140"/>
-      <c r="F19" s="113"/>
-      <c r="G19" s="113"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E19" s="154"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="33">
         <v>20003</v>
       </c>
@@ -12864,11 +12864,11 @@
       <c r="C20" s="34" t="s">
         <v>308</v>
       </c>
-      <c r="E20" s="140"/>
-      <c r="F20" s="113"/>
-      <c r="G20" s="113"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E20" s="154"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="119"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="33">
         <v>20003</v>
       </c>
@@ -12878,11 +12878,11 @@
       <c r="C21" s="34" t="s">
         <v>309</v>
       </c>
-      <c r="E21" s="140"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E21" s="154"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="119"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="33">
         <v>20003</v>
       </c>
@@ -12892,11 +12892,11 @@
       <c r="C22" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="E22" s="140"/>
-      <c r="F22" s="113"/>
-      <c r="G22" s="113"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E22" s="154"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>20003</v>
       </c>
@@ -12906,11 +12906,11 @@
       <c r="C23" s="34" t="s">
         <v>311</v>
       </c>
-      <c r="E23" s="140"/>
-      <c r="F23" s="113"/>
-      <c r="G23" s="113"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E23" s="154"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="119"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="33">
         <v>20003</v>
       </c>
@@ -12920,11 +12920,11 @@
       <c r="C24" s="34" t="s">
         <v>312</v>
       </c>
-      <c r="E24" s="140"/>
-      <c r="F24" s="113"/>
-      <c r="G24" s="113"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E24" s="154"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="33">
         <v>20003</v>
       </c>
@@ -12934,11 +12934,11 @@
       <c r="C25" s="34" t="s">
         <v>313</v>
       </c>
-      <c r="E25" s="140"/>
-      <c r="F25" s="113"/>
-      <c r="G25" s="113"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E25" s="154"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="33">
         <v>20003</v>
       </c>
@@ -12948,11 +12948,11 @@
       <c r="C26" s="34" t="s">
         <v>314</v>
       </c>
-      <c r="E26" s="140"/>
-      <c r="F26" s="113"/>
-      <c r="G26" s="113"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E26" s="154"/>
+      <c r="F26" s="119"/>
+      <c r="G26" s="119"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="33">
         <v>20003</v>
       </c>
@@ -12962,11 +12962,11 @@
       <c r="C27" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="E27" s="140"/>
-      <c r="F27" s="113"/>
-      <c r="G27" s="113"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E27" s="154"/>
+      <c r="F27" s="119"/>
+      <c r="G27" s="119"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="33">
         <v>20003</v>
       </c>
@@ -12976,11 +12976,11 @@
       <c r="C28" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="E28" s="140"/>
-      <c r="F28" s="113"/>
-      <c r="G28" s="113"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E28" s="154"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="119"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="33">
         <v>20003</v>
       </c>
@@ -12990,11 +12990,11 @@
       <c r="C29" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="E29" s="140"/>
-      <c r="F29" s="113"/>
-      <c r="G29" s="113"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E29" s="154"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="119"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="33">
         <v>20003</v>
       </c>
@@ -13004,11 +13004,11 @@
       <c r="C30" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="E30" s="140"/>
-      <c r="F30" s="113"/>
-      <c r="G30" s="113"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E30" s="154"/>
+      <c r="F30" s="119"/>
+      <c r="G30" s="119"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="33">
         <v>20003</v>
       </c>
@@ -13018,11 +13018,11 @@
       <c r="C31" s="34" t="s">
         <v>319</v>
       </c>
-      <c r="E31" s="140"/>
-      <c r="F31" s="113"/>
-      <c r="G31" s="113"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E31" s="154"/>
+      <c r="F31" s="119"/>
+      <c r="G31" s="119"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="33">
         <v>20003</v>
       </c>
@@ -13032,11 +13032,11 @@
       <c r="C32" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="E32" s="140"/>
-      <c r="F32" s="113"/>
-      <c r="G32" s="113"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E32" s="154"/>
+      <c r="F32" s="119"/>
+      <c r="G32" s="119"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>20003</v>
       </c>
@@ -13046,11 +13046,11 @@
       <c r="C33" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="E33" s="140"/>
-      <c r="F33" s="113"/>
-      <c r="G33" s="113"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E33" s="154"/>
+      <c r="F33" s="119"/>
+      <c r="G33" s="119"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="33">
         <v>20003</v>
       </c>
@@ -13060,11 +13060,11 @@
       <c r="C34" s="34" t="s">
         <v>322</v>
       </c>
-      <c r="E34" s="140"/>
-      <c r="F34" s="113"/>
-      <c r="G34" s="113"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E34" s="154"/>
+      <c r="F34" s="119"/>
+      <c r="G34" s="119"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="33">
         <v>20003</v>
       </c>
@@ -13074,11 +13074,11 @@
       <c r="C35" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="E35" s="140"/>
-      <c r="F35" s="113"/>
-      <c r="G35" s="113"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E35" s="154"/>
+      <c r="F35" s="119"/>
+      <c r="G35" s="119"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="33">
         <v>20003</v>
       </c>
@@ -13088,11 +13088,11 @@
       <c r="C36" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="E36" s="140"/>
-      <c r="F36" s="113"/>
-      <c r="G36" s="113"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E36" s="154"/>
+      <c r="F36" s="119"/>
+      <c r="G36" s="119"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="33">
         <v>20003</v>
       </c>
@@ -13102,11 +13102,11 @@
       <c r="C37" s="34" t="s">
         <v>325</v>
       </c>
-      <c r="E37" s="140"/>
-      <c r="F37" s="113"/>
-      <c r="G37" s="113"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E37" s="154"/>
+      <c r="F37" s="119"/>
+      <c r="G37" s="119"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="33">
         <v>20003</v>
       </c>
@@ -13116,11 +13116,11 @@
       <c r="C38" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="E38" s="140"/>
-      <c r="F38" s="113"/>
-      <c r="G38" s="113"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E38" s="154"/>
+      <c r="F38" s="119"/>
+      <c r="G38" s="119"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="33">
         <v>20003</v>
       </c>
@@ -13130,11 +13130,11 @@
       <c r="C39" s="34" t="s">
         <v>327</v>
       </c>
-      <c r="E39" s="140"/>
-      <c r="F39" s="113"/>
-      <c r="G39" s="113"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E39" s="154"/>
+      <c r="F39" s="119"/>
+      <c r="G39" s="119"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="33">
         <v>20003</v>
       </c>
@@ -13144,11 +13144,11 @@
       <c r="C40" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="E40" s="140"/>
-      <c r="F40" s="113"/>
-      <c r="G40" s="113"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="E40" s="154"/>
+      <c r="F40" s="119"/>
+      <c r="G40" s="119"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="33">
         <v>20003</v>
       </c>
@@ -13158,11 +13158,11 @@
       <c r="C41" s="34" t="s">
         <v>329</v>
       </c>
-      <c r="E41" s="140"/>
-      <c r="F41" s="113"/>
-      <c r="G41" s="113"/>
-    </row>
-    <row r="42" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E41" s="154"/>
+      <c r="F41" s="119"/>
+      <c r="G41" s="119"/>
+    </row>
+    <row r="42" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="33">
         <v>20003</v>
       </c>
@@ -13172,19 +13172,19 @@
       <c r="C42" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="E42" s="140"/>
-      <c r="F42" s="113"/>
-      <c r="G42" s="113"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A43" s="110" t="s">
+      <c r="E42" s="154"/>
+      <c r="F42" s="119"/>
+      <c r="G42" s="119"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="125" t="s">
         <v>1124</v>
       </c>
-      <c r="B43" s="111"/>
-      <c r="C43" s="112"/>
+      <c r="B43" s="126"/>
+      <c r="C43" s="127"/>
       <c r="D43" s="8"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
         <v>113</v>
       </c>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="D44" s="8"/>
     </row>
-    <row r="45" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="36">
         <v>30750</v>
       </c>
@@ -13209,20 +13209,20 @@
       <c r="E45" s="87">
         <v>16604</v>
       </c>
-      <c r="F45" s="134" t="s">
+      <c r="F45" s="153" t="s">
         <v>1134</v>
       </c>
-      <c r="G45" s="134"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A46" s="107" t="s">
+      <c r="G45" s="153"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="116" t="s">
         <v>1107</v>
       </c>
-      <c r="B46" s="108"/>
-      <c r="C46" s="109"/>
+      <c r="B46" s="117"/>
+      <c r="C46" s="118"/>
       <c r="D46" s="8"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="61" t="s">
         <v>95</v>
       </c>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="D47" s="8"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>332</v>
       </c>
@@ -13246,7 +13246,7 @@
       <c r="F48" s="87"/>
       <c r="G48" s="87"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>334</v>
       </c>
@@ -13260,7 +13260,7 @@
       <c r="F49" s="87"/>
       <c r="G49" s="87"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
         <v>336</v>
       </c>
@@ -13274,7 +13274,7 @@
       <c r="F50" s="87"/>
       <c r="G50" s="87"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
         <v>338</v>
       </c>
@@ -13288,7 +13288,7 @@
       <c r="F51" s="87"/>
       <c r="G51" s="87"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>340</v>
       </c>
@@ -13302,7 +13302,7 @@
       <c r="F52" s="87"/>
       <c r="G52" s="87"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
         <v>342</v>
       </c>
@@ -13316,7 +13316,7 @@
       <c r="F53" s="87"/>
       <c r="G53" s="87"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
         <v>344</v>
       </c>
@@ -13330,7 +13330,7 @@
       <c r="F54" s="87"/>
       <c r="G54" s="87"/>
     </row>
-    <row r="55" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
         <v>346</v>
       </c>
@@ -13344,7 +13344,7 @@
       <c r="F55" s="87"/>
       <c r="G55" s="87"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
         <v>348</v>
       </c>
@@ -13358,7 +13358,7 @@
       <c r="F56" s="87"/>
       <c r="G56" s="87"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
         <v>350</v>
       </c>
@@ -13372,7 +13372,7 @@
       <c r="F57" s="91"/>
       <c r="G57" s="91"/>
     </row>
-    <row r="58" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>352</v>
       </c>
@@ -13386,15 +13386,15 @@
       <c r="F58" s="91"/>
       <c r="G58" s="91"/>
     </row>
-    <row r="59" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="107" t="s">
+    <row r="59" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="116" t="s">
         <v>1108</v>
       </c>
-      <c r="B59" s="108"/>
-      <c r="C59" s="108"/>
-      <c r="D59" s="109"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="B59" s="117"/>
+      <c r="C59" s="117"/>
+      <c r="D59" s="118"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="24" t="s">
         <v>96</v>
       </c>
@@ -13406,7 +13406,7 @@
       </c>
       <c r="D60" s="63"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="39" t="s">
         <v>354</v>
       </c>
@@ -13423,7 +13423,7 @@
       <c r="F61" s="87"/>
       <c r="G61" s="87"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>356</v>
       </c>
@@ -13440,7 +13440,7 @@
       <c r="F62" s="87"/>
       <c r="G62" s="87"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
         <v>358</v>
       </c>
@@ -13457,7 +13457,7 @@
       <c r="F63" s="87"/>
       <c r="G63" s="87"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
         <v>360</v>
       </c>
@@ -13474,7 +13474,7 @@
       <c r="F64" s="87"/>
       <c r="G64" s="87"/>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
         <v>362</v>
       </c>
@@ -13491,7 +13491,7 @@
       <c r="F65" s="87"/>
       <c r="G65" s="87"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
         <v>364</v>
       </c>
@@ -13508,7 +13508,7 @@
       <c r="F66" s="87"/>
       <c r="G66" s="87"/>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
         <v>366</v>
       </c>
@@ -13525,7 +13525,7 @@
       <c r="F67" s="87"/>
       <c r="G67" s="87"/>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
         <v>368</v>
       </c>
@@ -13542,7 +13542,7 @@
       <c r="F68" s="87"/>
       <c r="G68" s="87"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
         <v>370</v>
       </c>
@@ -13559,7 +13559,7 @@
       <c r="F69" s="87"/>
       <c r="G69" s="87"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
         <v>372</v>
       </c>
@@ -13576,7 +13576,7 @@
       <c r="F70" s="87"/>
       <c r="G70" s="87"/>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
         <v>374</v>
       </c>
@@ -13593,7 +13593,7 @@
       <c r="F71" s="87"/>
       <c r="G71" s="87"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
         <v>374</v>
       </c>
@@ -13610,7 +13610,7 @@
       <c r="F72" s="87"/>
       <c r="G72" s="87"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
         <v>376</v>
       </c>
@@ -13627,7 +13627,7 @@
       <c r="F73" s="87"/>
       <c r="G73" s="87"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>376</v>
       </c>
@@ -13644,7 +13644,7 @@
       <c r="F74" s="87"/>
       <c r="G74" s="87"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
         <v>378</v>
       </c>
@@ -13661,7 +13661,7 @@
       <c r="F75" s="87"/>
       <c r="G75" s="87"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
         <v>378</v>
       </c>
@@ -13678,7 +13678,7 @@
       <c r="F76" s="87"/>
       <c r="G76" s="87"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>380</v>
       </c>
@@ -13695,7 +13695,7 @@
       <c r="F77" s="87"/>
       <c r="G77" s="87"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
         <v>382</v>
       </c>
@@ -13712,7 +13712,7 @@
       <c r="F78" s="87"/>
       <c r="G78" s="87"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>384</v>
       </c>
@@ -13729,7 +13729,7 @@
       <c r="F79" s="87"/>
       <c r="G79" s="87"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
         <v>386</v>
       </c>
@@ -13746,7 +13746,7 @@
       <c r="F80" s="87"/>
       <c r="G80" s="87"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
         <v>388</v>
       </c>
@@ -13763,7 +13763,7 @@
       <c r="F81" s="87"/>
       <c r="G81" s="87"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
         <v>390</v>
       </c>
@@ -13780,7 +13780,7 @@
       <c r="F82" s="87"/>
       <c r="G82" s="87"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
         <v>392</v>
       </c>
@@ -13797,7 +13797,7 @@
       <c r="F83" s="87"/>
       <c r="G83" s="87"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
         <v>394</v>
       </c>
@@ -13814,7 +13814,7 @@
       <c r="F84" s="87"/>
       <c r="G84" s="87"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>396</v>
       </c>
@@ -13831,7 +13831,7 @@
       <c r="F85" s="87"/>
       <c r="G85" s="87"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
         <v>398</v>
       </c>
@@ -13848,7 +13848,7 @@
       <c r="F86" s="87"/>
       <c r="G86" s="87"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
         <v>400</v>
       </c>
@@ -13865,7 +13865,7 @@
       <c r="F87" s="87"/>
       <c r="G87" s="87"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
         <v>402</v>
       </c>
@@ -13882,7 +13882,7 @@
       <c r="F88" s="87"/>
       <c r="G88" s="87"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
         <v>403</v>
       </c>
@@ -13899,7 +13899,7 @@
       <c r="F89" s="87"/>
       <c r="G89" s="87"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
         <v>404</v>
       </c>
@@ -13916,7 +13916,7 @@
       <c r="F90" s="87"/>
       <c r="G90" s="87"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>406</v>
       </c>
@@ -13933,7 +13933,7 @@
       <c r="F91" s="87"/>
       <c r="G91" s="87"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
         <v>408</v>
       </c>
@@ -13950,7 +13950,7 @@
       <c r="F92" s="87"/>
       <c r="G92" s="87"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
         <v>410</v>
       </c>
@@ -13967,7 +13967,7 @@
       <c r="F93" s="87"/>
       <c r="G93" s="87"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
         <v>412</v>
       </c>
@@ -13984,7 +13984,7 @@
       <c r="F94" s="87"/>
       <c r="G94" s="87"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
         <v>414</v>
       </c>
@@ -14001,7 +14001,7 @@
       <c r="F95" s="87"/>
       <c r="G95" s="87"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
         <v>416</v>
       </c>
@@ -14018,7 +14018,7 @@
       <c r="F96" s="87"/>
       <c r="G96" s="87"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="56" t="s">
         <v>418</v>
       </c>
@@ -14032,12 +14032,12 @@
       <c r="E97" s="87">
         <v>0</v>
       </c>
-      <c r="F97" s="113" t="s">
+      <c r="F97" s="119" t="s">
         <v>1141</v>
       </c>
-      <c r="G97" s="113"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G97" s="119"/>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="56" t="s">
         <v>420</v>
       </c>
@@ -14053,10 +14053,10 @@
       <c r="E98" s="87">
         <v>0</v>
       </c>
-      <c r="F98" s="113"/>
-      <c r="G98" s="113"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F98" s="119"/>
+      <c r="G98" s="119"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="56" t="s">
         <v>422</v>
       </c>
@@ -14072,10 +14072,10 @@
       <c r="E99" s="87">
         <v>0</v>
       </c>
-      <c r="F99" s="113"/>
-      <c r="G99" s="113"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F99" s="119"/>
+      <c r="G99" s="119"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="56" t="s">
         <v>424</v>
       </c>
@@ -14091,10 +14091,10 @@
       <c r="E100" s="87">
         <v>0</v>
       </c>
-      <c r="F100" s="113"/>
-      <c r="G100" s="113"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F100" s="119"/>
+      <c r="G100" s="119"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="56" t="s">
         <v>426</v>
       </c>
@@ -14108,10 +14108,10 @@
       <c r="E101" s="87">
         <v>0</v>
       </c>
-      <c r="F101" s="113"/>
-      <c r="G101" s="113"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F101" s="119"/>
+      <c r="G101" s="119"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="56" t="s">
         <v>427</v>
       </c>
@@ -14127,10 +14127,10 @@
       <c r="E102" s="87">
         <v>0</v>
       </c>
-      <c r="F102" s="113"/>
-      <c r="G102" s="113"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F102" s="119"/>
+      <c r="G102" s="119"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="56" t="s">
         <v>429</v>
       </c>
@@ -14146,10 +14146,10 @@
       <c r="E103" s="87">
         <v>0</v>
       </c>
-      <c r="F103" s="113"/>
-      <c r="G103" s="113"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F103" s="119"/>
+      <c r="G103" s="119"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="56" t="s">
         <v>431</v>
       </c>
@@ -14163,10 +14163,10 @@
       <c r="E104" s="87">
         <v>0</v>
       </c>
-      <c r="F104" s="113"/>
-      <c r="G104" s="113"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F104" s="119"/>
+      <c r="G104" s="119"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="56" t="s">
         <v>432</v>
       </c>
@@ -14182,10 +14182,10 @@
       <c r="E105" s="87">
         <v>0</v>
       </c>
-      <c r="F105" s="113"/>
-      <c r="G105" s="113"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F105" s="119"/>
+      <c r="G105" s="119"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="56" t="s">
         <v>434</v>
       </c>
@@ -14201,10 +14201,10 @@
       <c r="E106" s="87">
         <v>0</v>
       </c>
-      <c r="F106" s="113"/>
-      <c r="G106" s="113"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F106" s="119"/>
+      <c r="G106" s="119"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="56" t="s">
         <v>435</v>
       </c>
@@ -14220,10 +14220,10 @@
       <c r="E107" s="87">
         <v>0</v>
       </c>
-      <c r="F107" s="113"/>
-      <c r="G107" s="113"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F107" s="119"/>
+      <c r="G107" s="119"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="56" t="s">
         <v>437</v>
       </c>
@@ -14239,10 +14239,10 @@
       <c r="E108" s="87">
         <v>0</v>
       </c>
-      <c r="F108" s="113"/>
-      <c r="G108" s="113"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F108" s="119"/>
+      <c r="G108" s="119"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="56" t="s">
         <v>439</v>
       </c>
@@ -14258,10 +14258,10 @@
       <c r="E109" s="87">
         <v>0</v>
       </c>
-      <c r="F109" s="113"/>
-      <c r="G109" s="113"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F109" s="119"/>
+      <c r="G109" s="119"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="56" t="s">
         <v>441</v>
       </c>
@@ -14277,10 +14277,10 @@
       <c r="E110" s="87">
         <v>0</v>
       </c>
-      <c r="F110" s="113"/>
-      <c r="G110" s="113"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F110" s="119"/>
+      <c r="G110" s="119"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="56" t="s">
         <v>443</v>
       </c>
@@ -14296,10 +14296,10 @@
       <c r="E111" s="87">
         <v>0</v>
       </c>
-      <c r="F111" s="113"/>
-      <c r="G111" s="113"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F111" s="119"/>
+      <c r="G111" s="119"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="56" t="s">
         <v>445</v>
       </c>
@@ -14315,10 +14315,10 @@
       <c r="E112" s="87">
         <v>0</v>
       </c>
-      <c r="F112" s="113"/>
-      <c r="G112" s="113"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F112" s="119"/>
+      <c r="G112" s="119"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="56" t="s">
         <v>447</v>
       </c>
@@ -14332,10 +14332,10 @@
       <c r="E113" s="87">
         <v>0</v>
       </c>
-      <c r="F113" s="113"/>
-      <c r="G113" s="113"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F113" s="119"/>
+      <c r="G113" s="119"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="56" t="s">
         <v>449</v>
       </c>
@@ -14351,10 +14351,10 @@
       <c r="E114" s="87">
         <v>0</v>
       </c>
-      <c r="F114" s="113"/>
-      <c r="G114" s="113"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F114" s="119"/>
+      <c r="G114" s="119"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="57" t="s">
         <v>451</v>
       </c>
@@ -14370,10 +14370,10 @@
       <c r="E115" s="87">
         <v>0</v>
       </c>
-      <c r="F115" s="113"/>
-      <c r="G115" s="113"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F115" s="119"/>
+      <c r="G115" s="119"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="56" t="s">
         <v>452</v>
       </c>
@@ -14387,10 +14387,10 @@
       <c r="E116" s="87">
         <v>0</v>
       </c>
-      <c r="F116" s="113"/>
-      <c r="G116" s="113"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F116" s="119"/>
+      <c r="G116" s="119"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="57" t="s">
         <v>453</v>
       </c>
@@ -14406,10 +14406,10 @@
       <c r="E117" s="87">
         <v>0</v>
       </c>
-      <c r="F117" s="113"/>
-      <c r="G117" s="113"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F117" s="119"/>
+      <c r="G117" s="119"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="57" t="s">
         <v>454</v>
       </c>
@@ -14425,10 +14425,10 @@
       <c r="E118" s="87">
         <v>0</v>
       </c>
-      <c r="F118" s="113"/>
-      <c r="G118" s="113"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F118" s="119"/>
+      <c r="G118" s="119"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="57" t="s">
         <v>455</v>
       </c>
@@ -14442,10 +14442,10 @@
       <c r="E119" s="87">
         <v>13</v>
       </c>
-      <c r="F119" s="113"/>
-      <c r="G119" s="113"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F119" s="119"/>
+      <c r="G119" s="119"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="57" t="s">
         <v>456</v>
       </c>
@@ -14461,10 +14461,10 @@
       <c r="E120" s="87">
         <v>0</v>
       </c>
-      <c r="F120" s="113"/>
-      <c r="G120" s="113"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F120" s="119"/>
+      <c r="G120" s="119"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="57" t="s">
         <v>458</v>
       </c>
@@ -14480,10 +14480,10 @@
       <c r="E121" s="87">
         <v>0</v>
       </c>
-      <c r="F121" s="113"/>
-      <c r="G121" s="113"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F121" s="119"/>
+      <c r="G121" s="119"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="57" t="s">
         <v>460</v>
       </c>
@@ -14499,10 +14499,10 @@
       <c r="E122" s="87">
         <v>1</v>
       </c>
-      <c r="F122" s="113"/>
-      <c r="G122" s="113"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F122" s="119"/>
+      <c r="G122" s="119"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="57" t="s">
         <v>462</v>
       </c>
@@ -14518,10 +14518,10 @@
       <c r="E123" s="87">
         <v>31</v>
       </c>
-      <c r="F123" s="113"/>
-      <c r="G123" s="113"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F123" s="119"/>
+      <c r="G123" s="119"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="58" t="s">
         <v>464</v>
       </c>
@@ -14537,10 +14537,10 @@
       <c r="E124" s="87">
         <v>1</v>
       </c>
-      <c r="F124" s="113"/>
-      <c r="G124" s="113"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F124" s="119"/>
+      <c r="G124" s="119"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="58" t="s">
         <v>467</v>
       </c>
@@ -14556,10 +14556,10 @@
       <c r="E125" s="87">
         <v>0</v>
       </c>
-      <c r="F125" s="113"/>
-      <c r="G125" s="113"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F125" s="119"/>
+      <c r="G125" s="119"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="58" t="s">
         <v>469</v>
       </c>
@@ -14575,10 +14575,10 @@
       <c r="E126" s="87">
         <v>0</v>
       </c>
-      <c r="F126" s="113"/>
-      <c r="G126" s="113"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F126" s="119"/>
+      <c r="G126" s="119"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="58" t="s">
         <v>471</v>
       </c>
@@ -14594,10 +14594,10 @@
       <c r="E127" s="87">
         <v>0</v>
       </c>
-      <c r="F127" s="113"/>
-      <c r="G127" s="113"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F127" s="119"/>
+      <c r="G127" s="119"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="58" t="s">
         <v>473</v>
       </c>
@@ -14613,10 +14613,10 @@
       <c r="E128" s="87">
         <v>0</v>
       </c>
-      <c r="F128" s="113"/>
-      <c r="G128" s="113"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F128" s="119"/>
+      <c r="G128" s="119"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="58" t="s">
         <v>475</v>
       </c>
@@ -14632,10 +14632,10 @@
       <c r="E129" s="87">
         <v>0</v>
       </c>
-      <c r="F129" s="113"/>
-      <c r="G129" s="113"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F129" s="119"/>
+      <c r="G129" s="119"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="58" t="s">
         <v>477</v>
       </c>
@@ -14651,10 +14651,10 @@
       <c r="E130" s="87">
         <v>0</v>
       </c>
-      <c r="F130" s="113"/>
-      <c r="G130" s="113"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F130" s="119"/>
+      <c r="G130" s="119"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="58" t="s">
         <v>479</v>
       </c>
@@ -14670,10 +14670,10 @@
       <c r="E131" s="87">
         <v>0</v>
       </c>
-      <c r="F131" s="113"/>
-      <c r="G131" s="113"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F131" s="119"/>
+      <c r="G131" s="119"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="58" t="s">
         <v>481</v>
       </c>
@@ -14689,10 +14689,10 @@
       <c r="E132" s="87">
         <v>0</v>
       </c>
-      <c r="F132" s="113"/>
-      <c r="G132" s="113"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F132" s="119"/>
+      <c r="G132" s="119"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="58" t="s">
         <v>483</v>
       </c>
@@ -14708,10 +14708,10 @@
       <c r="E133" s="87">
         <v>0</v>
       </c>
-      <c r="F133" s="113"/>
-      <c r="G133" s="113"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F133" s="119"/>
+      <c r="G133" s="119"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="58" t="s">
         <v>485</v>
       </c>
@@ -14727,10 +14727,10 @@
       <c r="E134" s="87">
         <v>0</v>
       </c>
-      <c r="F134" s="113"/>
-      <c r="G134" s="113"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F134" s="119"/>
+      <c r="G134" s="119"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="59" t="s">
         <v>487</v>
       </c>
@@ -14746,10 +14746,10 @@
       <c r="E135" s="87">
         <v>0</v>
       </c>
-      <c r="F135" s="113"/>
-      <c r="G135" s="113"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F135" s="119"/>
+      <c r="G135" s="119"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="59" t="s">
         <v>489</v>
       </c>
@@ -14765,10 +14765,10 @@
       <c r="E136" s="87">
         <v>0</v>
       </c>
-      <c r="F136" s="113"/>
-      <c r="G136" s="113"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F136" s="119"/>
+      <c r="G136" s="119"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="59" t="s">
         <v>491</v>
       </c>
@@ -14784,10 +14784,10 @@
       <c r="E137" s="87">
         <v>0</v>
       </c>
-      <c r="F137" s="113"/>
-      <c r="G137" s="113"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F137" s="119"/>
+      <c r="G137" s="119"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="59" t="s">
         <v>493</v>
       </c>
@@ -14803,10 +14803,10 @@
       <c r="E138" s="87">
         <v>0</v>
       </c>
-      <c r="F138" s="113"/>
-      <c r="G138" s="113"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F138" s="119"/>
+      <c r="G138" s="119"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="59" t="s">
         <v>495</v>
       </c>
@@ -14820,10 +14820,10 @@
       <c r="E139" s="87">
         <v>10</v>
       </c>
-      <c r="F139" s="113"/>
-      <c r="G139" s="113"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F139" s="119"/>
+      <c r="G139" s="119"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="59" t="s">
         <v>496</v>
       </c>
@@ -14839,10 +14839,10 @@
       <c r="E140" s="87">
         <v>0</v>
       </c>
-      <c r="F140" s="113"/>
-      <c r="G140" s="113"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F140" s="119"/>
+      <c r="G140" s="119"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="59" t="s">
         <v>498</v>
       </c>
@@ -14858,10 +14858,10 @@
       <c r="E141" s="87">
         <v>0</v>
       </c>
-      <c r="F141" s="113"/>
-      <c r="G141" s="113"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F141" s="119"/>
+      <c r="G141" s="119"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="59" t="s">
         <v>500</v>
       </c>
@@ -14877,10 +14877,10 @@
       <c r="E142" s="87">
         <v>0</v>
       </c>
-      <c r="F142" s="113"/>
-      <c r="G142" s="113"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F142" s="119"/>
+      <c r="G142" s="119"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="59" t="s">
         <v>464</v>
       </c>
@@ -14896,10 +14896,10 @@
       <c r="E143" s="87">
         <v>1</v>
       </c>
-      <c r="F143" s="113"/>
-      <c r="G143" s="113"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F143" s="119"/>
+      <c r="G143" s="119"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="59" t="s">
         <v>467</v>
       </c>
@@ -14915,10 +14915,10 @@
       <c r="E144" s="87">
         <v>0</v>
       </c>
-      <c r="F144" s="113"/>
-      <c r="G144" s="113"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F144" s="119"/>
+      <c r="G144" s="119"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="59" t="s">
         <v>502</v>
       </c>
@@ -14932,10 +14932,10 @@
       <c r="E145" s="87">
         <v>1</v>
       </c>
-      <c r="F145" s="113"/>
-      <c r="G145" s="113"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F145" s="119"/>
+      <c r="G145" s="119"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="59" t="s">
         <v>503</v>
       </c>
@@ -14951,10 +14951,10 @@
       <c r="E146" s="87">
         <v>0</v>
       </c>
-      <c r="F146" s="113"/>
-      <c r="G146" s="113"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F146" s="119"/>
+      <c r="G146" s="119"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="59" t="s">
         <v>505</v>
       </c>
@@ -14970,10 +14970,10 @@
       <c r="E147" s="87">
         <v>0</v>
       </c>
-      <c r="F147" s="113"/>
-      <c r="G147" s="113"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F147" s="119"/>
+      <c r="G147" s="119"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="59" t="s">
         <v>506</v>
       </c>
@@ -14987,10 +14987,10 @@
       <c r="E148" s="87">
         <v>0</v>
       </c>
-      <c r="F148" s="113"/>
-      <c r="G148" s="113"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F148" s="119"/>
+      <c r="G148" s="119"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="59" t="s">
         <v>507</v>
       </c>
@@ -15006,10 +15006,10 @@
       <c r="E149" s="87">
         <v>0</v>
       </c>
-      <c r="F149" s="113"/>
-      <c r="G149" s="113"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F149" s="119"/>
+      <c r="G149" s="119"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="59" t="s">
         <v>509</v>
       </c>
@@ -15025,10 +15025,10 @@
       <c r="E150" s="87">
         <v>0</v>
       </c>
-      <c r="F150" s="113"/>
-      <c r="G150" s="113"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F150" s="119"/>
+      <c r="G150" s="119"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="59" t="s">
         <v>511</v>
       </c>
@@ -15044,10 +15044,10 @@
       <c r="E151" s="87">
         <v>0</v>
       </c>
-      <c r="F151" s="113"/>
-      <c r="G151" s="113"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F151" s="119"/>
+      <c r="G151" s="119"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="59" t="s">
         <v>513</v>
       </c>
@@ -15061,10 +15061,10 @@
       <c r="E152" s="87">
         <v>16</v>
       </c>
-      <c r="F152" s="113"/>
-      <c r="G152" s="113"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F152" s="119"/>
+      <c r="G152" s="119"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="59" t="s">
         <v>514</v>
       </c>
@@ -15080,10 +15080,10 @@
       <c r="E153" s="87">
         <v>0</v>
       </c>
-      <c r="F153" s="113"/>
-      <c r="G153" s="113"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F153" s="119"/>
+      <c r="G153" s="119"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="59" t="s">
         <v>515</v>
       </c>
@@ -15099,10 +15099,10 @@
       <c r="E154" s="87">
         <v>1</v>
       </c>
-      <c r="F154" s="113"/>
-      <c r="G154" s="113"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F154" s="119"/>
+      <c r="G154" s="119"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="59" t="s">
         <v>516</v>
       </c>
@@ -15118,10 +15118,10 @@
       <c r="E155" s="87">
         <v>0</v>
       </c>
-      <c r="F155" s="113"/>
-      <c r="G155" s="113"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F155" s="119"/>
+      <c r="G155" s="119"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="59" t="s">
         <v>518</v>
       </c>
@@ -15137,10 +15137,10 @@
       <c r="E156" s="87">
         <v>0</v>
       </c>
-      <c r="F156" s="113"/>
-      <c r="G156" s="113"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F156" s="119"/>
+      <c r="G156" s="119"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="56" t="s">
         <v>520</v>
       </c>
@@ -15156,10 +15156,10 @@
       <c r="E157" s="87">
         <v>0</v>
       </c>
-      <c r="F157" s="113"/>
-      <c r="G157" s="113"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F157" s="119"/>
+      <c r="G157" s="119"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="56" t="s">
         <v>522</v>
       </c>
@@ -15175,10 +15175,10 @@
       <c r="E158" s="87">
         <v>0</v>
       </c>
-      <c r="F158" s="113"/>
-      <c r="G158" s="113"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F158" s="119"/>
+      <c r="G158" s="119"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="56" t="s">
         <v>525</v>
       </c>
@@ -15194,10 +15194,10 @@
       <c r="E159" s="87">
         <v>0</v>
       </c>
-      <c r="F159" s="113"/>
-      <c r="G159" s="113"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F159" s="119"/>
+      <c r="G159" s="119"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="56" t="s">
         <v>526</v>
       </c>
@@ -15211,10 +15211,10 @@
       <c r="E160" s="87">
         <v>0</v>
       </c>
-      <c r="F160" s="113"/>
-      <c r="G160" s="113"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F160" s="119"/>
+      <c r="G160" s="119"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="56" t="s">
         <v>527</v>
       </c>
@@ -15230,10 +15230,10 @@
       <c r="E161" s="87">
         <v>0</v>
       </c>
-      <c r="F161" s="113"/>
-      <c r="G161" s="113"/>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F161" s="119"/>
+      <c r="G161" s="119"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="56" t="s">
         <v>529</v>
       </c>
@@ -15249,10 +15249,10 @@
       <c r="E162" s="87">
         <v>0</v>
       </c>
-      <c r="F162" s="113"/>
-      <c r="G162" s="113"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F162" s="119"/>
+      <c r="G162" s="119"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="56" t="s">
         <v>531</v>
       </c>
@@ -15268,10 +15268,10 @@
       <c r="E163" s="87">
         <v>0</v>
       </c>
-      <c r="F163" s="113"/>
-      <c r="G163" s="113"/>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="F163" s="119"/>
+      <c r="G163" s="119"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="56" t="s">
         <v>533</v>
       </c>
@@ -15287,10 +15287,10 @@
       <c r="E164" s="87">
         <v>0</v>
       </c>
-      <c r="F164" s="113"/>
-      <c r="G164" s="113"/>
-    </row>
-    <row r="165" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F164" s="119"/>
+      <c r="G164" s="119"/>
+    </row>
+    <row r="165" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="56" t="s">
         <v>534</v>
       </c>
@@ -15309,7 +15309,7 @@
       <c r="F165" s="92"/>
       <c r="G165" s="92"/>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="56" t="s">
         <v>535</v>
       </c>
@@ -15328,7 +15328,7 @@
       <c r="F166" s="92"/>
       <c r="G166" s="92"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="56" t="s">
         <v>538</v>
       </c>
@@ -15347,7 +15347,7 @@
       <c r="F167" s="92"/>
       <c r="G167" s="92"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="56" t="s">
         <v>540</v>
       </c>
@@ -15366,7 +15366,7 @@
       <c r="F168" s="92"/>
       <c r="G168" s="92"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="56" t="s">
         <v>542</v>
       </c>
@@ -15385,7 +15385,7 @@
       <c r="F169" s="92"/>
       <c r="G169" s="92"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="56" t="s">
         <v>544</v>
       </c>
@@ -15404,7 +15404,7 @@
       <c r="F170" s="92"/>
       <c r="G170" s="92"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="56" t="s">
         <v>546</v>
       </c>
@@ -15423,7 +15423,7 @@
       <c r="F171" s="92"/>
       <c r="G171" s="92"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="56" t="s">
         <v>548</v>
       </c>
@@ -15442,7 +15442,7 @@
       <c r="F172" s="92"/>
       <c r="G172" s="92"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="56" t="s">
         <v>550</v>
       </c>
@@ -15461,7 +15461,7 @@
       <c r="F173" s="92"/>
       <c r="G173" s="92"/>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="56" t="s">
         <v>552</v>
       </c>
@@ -15480,7 +15480,7 @@
       <c r="F174" s="92"/>
       <c r="G174" s="92"/>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="56" t="s">
         <v>554</v>
       </c>
@@ -15499,7 +15499,7 @@
       <c r="F175" s="92"/>
       <c r="G175" s="92"/>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="56" t="s">
         <v>556</v>
       </c>
@@ -15518,7 +15518,7 @@
       <c r="F176" s="92"/>
       <c r="G176" s="92"/>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="56" t="s">
         <v>558</v>
       </c>
@@ -15537,7 +15537,7 @@
       <c r="F177" s="92"/>
       <c r="G177" s="92"/>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="56" t="s">
         <v>559</v>
       </c>
@@ -15556,7 +15556,7 @@
       <c r="F178" s="92"/>
       <c r="G178" s="92"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="56" t="s">
         <v>560</v>
       </c>
@@ -15575,7 +15575,7 @@
       <c r="F179" s="92"/>
       <c r="G179" s="92"/>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="56" t="s">
         <v>561</v>
       </c>
@@ -15594,7 +15594,7 @@
       <c r="F180" s="92"/>
       <c r="G180" s="92"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="56" t="s">
         <v>562</v>
       </c>
@@ -15613,7 +15613,7 @@
       <c r="F181" s="92"/>
       <c r="G181" s="92"/>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="56" t="s">
         <v>563</v>
       </c>
@@ -15632,7 +15632,7 @@
       <c r="F182" s="92"/>
       <c r="G182" s="92"/>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="56" t="s">
         <v>565</v>
       </c>
@@ -15651,7 +15651,7 @@
       <c r="F183" s="92"/>
       <c r="G183" s="92"/>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="56" t="s">
         <v>567</v>
       </c>
@@ -15670,7 +15670,7 @@
       <c r="F184" s="92"/>
       <c r="G184" s="92"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="56" t="s">
         <v>569</v>
       </c>
@@ -15689,7 +15689,7 @@
       <c r="F185" s="92"/>
       <c r="G185" s="92"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="56" t="s">
         <v>571</v>
       </c>
@@ -15708,7 +15708,7 @@
       <c r="F186" s="92"/>
       <c r="G186" s="92"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="56" t="s">
         <v>573</v>
       </c>
@@ -15727,7 +15727,7 @@
       <c r="F187" s="92"/>
       <c r="G187" s="92"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="56" t="s">
         <v>574</v>
       </c>
@@ -15746,7 +15746,7 @@
       <c r="F188" s="92"/>
       <c r="G188" s="92"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="56" t="s">
         <v>575</v>
       </c>
@@ -15765,7 +15765,7 @@
       <c r="F189" s="92"/>
       <c r="G189" s="92"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="56" t="s">
         <v>577</v>
       </c>
@@ -15784,7 +15784,7 @@
       <c r="F190" s="92"/>
       <c r="G190" s="92"/>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="56" t="s">
         <v>579</v>
       </c>
@@ -15803,7 +15803,7 @@
       <c r="F191" s="92"/>
       <c r="G191" s="92"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="56" t="s">
         <v>582</v>
       </c>
@@ -15822,7 +15822,7 @@
       <c r="F192" s="92"/>
       <c r="G192" s="92"/>
     </row>
-    <row r="193" spans="1:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="60" t="s">
         <v>584</v>
       </c>
@@ -15841,18 +15841,22 @@
       <c r="F193" s="92"/>
       <c r="G193" s="92"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="46"/>
       <c r="B194" s="46"/>
       <c r="C194" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="Y7:AB7"/>
-    <mergeCell ref="Y8:Z9"/>
-    <mergeCell ref="AA8:AB8"/>
-    <mergeCell ref="AA9:AB9"/>
-    <mergeCell ref="F97:G130"/>
+    <mergeCell ref="E9:E42"/>
+    <mergeCell ref="M7:P7"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="F131:G164"/>
     <mergeCell ref="S7:V7"/>
     <mergeCell ref="S8:T9"/>
@@ -15861,17 +15865,13 @@
     <mergeCell ref="M8:N9"/>
     <mergeCell ref="O8:P8"/>
     <mergeCell ref="O9:P9"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A43:C43"/>
     <mergeCell ref="F9:G42"/>
     <mergeCell ref="F45:G45"/>
-    <mergeCell ref="E9:E42"/>
-    <mergeCell ref="M7:P7"/>
+    <mergeCell ref="Y7:AB7"/>
+    <mergeCell ref="Y8:Z9"/>
+    <mergeCell ref="AA8:AB8"/>
+    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="F97:G130"/>
   </mergeCells>
   <conditionalFormatting sqref="F165:G193">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
